--- a/data/premier_league_raw_match_data.xlsx
+++ b/data/premier_league_raw_match_data.xlsx
@@ -5,22 +5,23 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Downloads\Nowy folder\112\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Desktop\InStatsWeTrust\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B136C811-3BB4-470B-8DFE-0971E06846D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9347771-FD1F-4E20-9650-21526F05ED8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27210" yWindow="3360" windowWidth="25875" windowHeight="13455" xr2:uid="{0FE85BFC-2024-4027-B3AD-B7D6B58B61DA}"/>
+    <workbookView xWindow="-28245" yWindow="2325" windowWidth="25875" windowHeight="13455" xr2:uid="{0FE85BFC-2024-4027-B3AD-B7D6B58B61DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="102">
   <si>
     <t>Manchester City</t>
   </si>
@@ -273,6 +274,60 @@
   <si>
     <t>Round</t>
   </si>
+  <si>
+    <t>Etihad Stadium</t>
+  </si>
+  <si>
+    <t>Craig Pawson</t>
+  </si>
+  <si>
+    <t>Match Report</t>
+  </si>
+  <si>
+    <t>Emirates Stadium</t>
+  </si>
+  <si>
+    <t>Michael Salisbury</t>
+  </si>
+  <si>
+    <t>Stamford Bridge</t>
+  </si>
+  <si>
+    <t>Chris Kavanagh</t>
+  </si>
+  <si>
+    <t>The American Express Stadium</t>
+  </si>
+  <si>
+    <t>Darren England</t>
+  </si>
+  <si>
+    <t>Molineux Stadium</t>
+  </si>
+  <si>
+    <t>Samuel Barrott</t>
+  </si>
+  <si>
+    <t>St Mary's Stadium</t>
+  </si>
+  <si>
+    <t>Tony Harrington</t>
+  </si>
+  <si>
+    <t>St James' Park</t>
+  </si>
+  <si>
+    <t>Vitality Stadium</t>
+  </si>
+  <si>
+    <t>Peter Bankes</t>
+  </si>
+  <si>
+    <t>Anfield</t>
+  </si>
+  <si>
+    <t>Thomas Bramall</t>
+  </si>
 </sst>
 </file>
 
@@ -306,9 +361,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -643,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A647DF9E-0117-4165-BE47-DD1C6849A118}">
-  <dimension ref="A1:I331"/>
+  <dimension ref="A1:J340"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
@@ -9935,7 +9991,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>29</v>
       </c>
@@ -9964,7 +10020,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>33</v>
       </c>
@@ -9993,7 +10049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>33</v>
       </c>
@@ -10022,7 +10078,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>33</v>
       </c>
@@ -10051,7 +10107,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>33</v>
       </c>
@@ -10080,7 +10136,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>33</v>
       </c>
@@ -10109,7 +10165,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>33</v>
       </c>
@@ -10138,7 +10194,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>33</v>
       </c>
@@ -10167,7 +10223,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>33</v>
       </c>
@@ -10196,7 +10252,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>33</v>
       </c>
@@ -10225,7 +10281,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>33</v>
       </c>
@@ -10253,9 +10309,658 @@
       <c r="I331" t="s">
         <v>21</v>
       </c>
+    </row>
+    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>34</v>
+      </c>
+      <c r="B332" t="s">
+        <v>64</v>
+      </c>
+      <c r="C332" s="1">
+        <v>45769</v>
+      </c>
+      <c r="D332" t="s">
+        <v>6</v>
+      </c>
+      <c r="E332" t="s">
+        <v>0</v>
+      </c>
+      <c r="F332">
+        <v>1.3</v>
+      </c>
+      <c r="G332" t="s">
+        <v>32</v>
+      </c>
+      <c r="H332">
+        <v>1.8</v>
+      </c>
+      <c r="I332" t="s">
+        <v>1</v>
+      </c>
+      <c r="J332" s="2"/>
+    </row>
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>34</v>
+      </c>
+      <c r="B333" t="s">
+        <v>67</v>
+      </c>
+      <c r="C333" s="1">
+        <v>45770</v>
+      </c>
+      <c r="D333" t="s">
+        <v>6</v>
+      </c>
+      <c r="E333" t="s">
+        <v>2</v>
+      </c>
+      <c r="F333">
+        <v>1.2</v>
+      </c>
+      <c r="G333" t="s">
+        <v>53</v>
+      </c>
+      <c r="H333">
+        <v>1.7</v>
+      </c>
+      <c r="I333" t="s">
+        <v>33</v>
+      </c>
+      <c r="J333" s="2"/>
+    </row>
+    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>34</v>
+      </c>
+      <c r="B334" t="s">
+        <v>10</v>
+      </c>
+      <c r="C334" s="1">
+        <v>45773</v>
+      </c>
+      <c r="D334" t="s">
+        <v>11</v>
+      </c>
+      <c r="E334" t="s">
+        <v>35</v>
+      </c>
+      <c r="F334">
+        <v>0.8</v>
+      </c>
+      <c r="G334" t="s">
+        <v>8</v>
+      </c>
+      <c r="H334">
+        <v>0.4</v>
+      </c>
+      <c r="I334" t="s">
+        <v>18</v>
+      </c>
+      <c r="J334" s="2"/>
+    </row>
+    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A335">
+        <v>34</v>
+      </c>
+      <c r="B335" t="s">
+        <v>10</v>
+      </c>
+      <c r="C335" s="1">
+        <v>45773</v>
+      </c>
+      <c r="D335" t="s">
+        <v>15</v>
+      </c>
+      <c r="E335" t="s">
+        <v>20</v>
+      </c>
+      <c r="F335">
+        <v>1.3</v>
+      </c>
+      <c r="G335" t="s">
+        <v>55</v>
+      </c>
+      <c r="H335">
+        <v>1.3</v>
+      </c>
+      <c r="I335" t="s">
+        <v>27</v>
+      </c>
+      <c r="J335" s="2"/>
+    </row>
+    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A336">
+        <v>34</v>
+      </c>
+      <c r="B336" t="s">
+        <v>10</v>
+      </c>
+      <c r="C336" s="1">
+        <v>45773</v>
+      </c>
+      <c r="D336" t="s">
+        <v>15</v>
+      </c>
+      <c r="E336" t="s">
+        <v>25</v>
+      </c>
+      <c r="F336">
+        <v>2</v>
+      </c>
+      <c r="G336" t="s">
+        <v>56</v>
+      </c>
+      <c r="H336">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I336" t="s">
+        <v>37</v>
+      </c>
+      <c r="J336" s="2"/>
+    </row>
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>34</v>
+      </c>
+      <c r="B337" t="s">
+        <v>10</v>
+      </c>
+      <c r="C337" s="1">
+        <v>45773</v>
+      </c>
+      <c r="D337" t="s">
+        <v>15</v>
+      </c>
+      <c r="E337" t="s">
+        <v>17</v>
+      </c>
+      <c r="F337">
+        <v>0.6</v>
+      </c>
+      <c r="G337" t="s">
+        <v>28</v>
+      </c>
+      <c r="H337">
+        <v>2.4</v>
+      </c>
+      <c r="I337" t="s">
+        <v>9</v>
+      </c>
+      <c r="J337" s="2"/>
+    </row>
+    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <v>34</v>
+      </c>
+      <c r="B338" t="s">
+        <v>10</v>
+      </c>
+      <c r="C338" s="1">
+        <v>45773</v>
+      </c>
+      <c r="D338" t="s">
+        <v>15</v>
+      </c>
+      <c r="E338" t="s">
+        <v>16</v>
+      </c>
+      <c r="F338">
+        <v>2.4</v>
+      </c>
+      <c r="G338" t="s">
+        <v>56</v>
+      </c>
+      <c r="H338">
+        <v>0.1</v>
+      </c>
+      <c r="I338" t="s">
+        <v>12</v>
+      </c>
+      <c r="J338" s="2"/>
+    </row>
+    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>34</v>
+      </c>
+      <c r="B339" t="s">
+        <v>29</v>
+      </c>
+      <c r="C339" s="1">
+        <v>45774</v>
+      </c>
+      <c r="D339" t="s">
+        <v>30</v>
+      </c>
+      <c r="E339" t="s">
+        <v>23</v>
+      </c>
+      <c r="F339">
+        <v>0.5</v>
+      </c>
+      <c r="G339" t="s">
+        <v>22</v>
+      </c>
+      <c r="H339">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I339" t="s">
+        <v>7</v>
+      </c>
+      <c r="J339" s="2"/>
+    </row>
+    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <v>34</v>
+      </c>
+      <c r="B340" t="s">
+        <v>29</v>
+      </c>
+      <c r="C340" s="1">
+        <v>45774</v>
+      </c>
+      <c r="D340" t="s">
+        <v>34</v>
+      </c>
+      <c r="E340" t="s">
+        <v>14</v>
+      </c>
+      <c r="F340">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G340" t="s">
+        <v>81</v>
+      </c>
+      <c r="H340">
+        <v>0.5</v>
+      </c>
+      <c r="I340" t="s">
+        <v>38</v>
+      </c>
+      <c r="J340" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F15253A6-5A08-48CB-B2F0-10236C66CD3C}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>34</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="1">
+        <v>45769</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1">
+        <v>1.3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1">
+        <v>1.8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="2">
+        <v>51834</v>
+      </c>
+      <c r="K1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L1" t="s">
+        <v>85</v>
+      </c>
+      <c r="M1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="1">
+        <v>45770</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1.2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2">
+        <v>1.7</v>
+      </c>
+      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="2">
+        <v>60167</v>
+      </c>
+      <c r="K2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1">
+        <v>45773</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3">
+        <v>0.8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>0.4</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="2">
+        <v>39894</v>
+      </c>
+      <c r="K3" t="s">
+        <v>89</v>
+      </c>
+      <c r="L3" t="s">
+        <v>90</v>
+      </c>
+      <c r="M3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1">
+        <v>45773</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>1.3</v>
+      </c>
+      <c r="G4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4">
+        <v>1.3</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="2">
+        <v>31499</v>
+      </c>
+      <c r="K4" t="s">
+        <v>91</v>
+      </c>
+      <c r="L4" t="s">
+        <v>92</v>
+      </c>
+      <c r="M4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1">
+        <v>45773</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="2">
+        <v>31518</v>
+      </c>
+      <c r="K5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L5" t="s">
+        <v>94</v>
+      </c>
+      <c r="M5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1">
+        <v>45773</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6">
+        <v>0.6</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6">
+        <v>2.4</v>
+      </c>
+      <c r="I6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="2">
+        <v>28946</v>
+      </c>
+      <c r="K6" t="s">
+        <v>95</v>
+      </c>
+      <c r="L6" t="s">
+        <v>96</v>
+      </c>
+      <c r="M6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45773</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>2.4</v>
+      </c>
+      <c r="G7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7">
+        <v>0.1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="2">
+        <v>52171</v>
+      </c>
+      <c r="K7" t="s">
+        <v>97</v>
+      </c>
+      <c r="L7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="1">
+        <v>45774</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8">
+        <v>0.5</v>
+      </c>
+      <c r="G8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I8" t="s">
+        <v>7</v>
+      </c>
+      <c r="J8" s="2">
+        <v>11241</v>
+      </c>
+      <c r="K8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45774</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9">
+        <v>0.5</v>
+      </c>
+      <c r="I9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" s="2">
+        <v>60415</v>
+      </c>
+      <c r="K9" t="s">
+        <v>100</v>
+      </c>
+      <c r="L9" t="s">
+        <v>101</v>
+      </c>
+      <c r="M9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/premier_league_raw_match_data.xlsx
+++ b/data/premier_league_raw_match_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Desktop\InStatsWeTrust\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9347771-FD1F-4E20-9650-21526F05ED8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487575A5-4331-40B3-BAE5-B01D671FAF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28245" yWindow="2325" windowWidth="25875" windowHeight="13455" xr2:uid="{0FE85BFC-2024-4027-B3AD-B7D6B58B61DA}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21150" xr2:uid="{0FE85BFC-2024-4027-B3AD-B7D6B58B61DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="104">
   <si>
     <t>Manchester City</t>
   </si>
@@ -327,6 +327,12 @@
   </si>
   <si>
     <t>Thomas Bramall</t>
+  </si>
+  <si>
+    <t>Goals_For</t>
+  </si>
+  <si>
+    <t>Goals_Against</t>
   </si>
 </sst>
 </file>
@@ -699,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A647DF9E-0117-4165-BE47-DD1C6849A118}">
-  <dimension ref="A1:J340"/>
+  <dimension ref="A1:L341"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
@@ -708,10 +714,12 @@
     <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>83</v>
       </c>
@@ -734,13 +742,19 @@
         <v>43</v>
       </c>
       <c r="H1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J1" t="s">
         <v>42</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -763,13 +777,19 @@
         <v>8</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
         <v>0.4</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -792,13 +812,19 @@
         <v>13</v>
       </c>
       <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
         <v>2.6</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -821,13 +847,19 @@
         <v>8</v>
       </c>
       <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>1.8</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -850,13 +882,19 @@
         <v>19</v>
       </c>
       <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
         <v>1.4</v>
       </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -879,13 +917,19 @@
         <v>22</v>
       </c>
       <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>1.2</v>
       </c>
-      <c r="I6" t="s">
+      <c r="K6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
@@ -908,13 +952,19 @@
         <v>24</v>
       </c>
       <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>0.5</v>
       </c>
-      <c r="I7" t="s">
+      <c r="K7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -937,13 +987,19 @@
         <v>28</v>
       </c>
       <c r="H8">
-        <v>2</v>
-      </c>
-      <c r="I8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1</v>
       </c>
@@ -966,13 +1022,19 @@
         <v>32</v>
       </c>
       <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
         <v>1.2</v>
       </c>
-      <c r="I9" t="s">
+      <c r="K9" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1</v>
       </c>
@@ -995,13 +1057,19 @@
         <v>13</v>
       </c>
       <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
         <v>0.8</v>
       </c>
-      <c r="I10" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1</v>
       </c>
@@ -1024,13 +1092,19 @@
         <v>22</v>
       </c>
       <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
         <v>1.2</v>
       </c>
-      <c r="I11" t="s">
+      <c r="K11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1053,13 +1127,19 @@
         <v>32</v>
       </c>
       <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
         <v>1.4</v>
       </c>
-      <c r="I12" t="s">
+      <c r="K12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1082,13 +1162,19 @@
         <v>44</v>
       </c>
       <c r="H13">
+        <v>4</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
         <v>0.3</v>
       </c>
-      <c r="I13" t="s">
+      <c r="K13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1111,13 +1197,19 @@
         <v>45</v>
       </c>
       <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I14" t="s">
+      <c r="K14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1140,13 +1232,19 @@
         <v>46</v>
       </c>
       <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1169,13 +1267,19 @@
         <v>32</v>
       </c>
       <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
         <v>0.6</v>
       </c>
-      <c r="I16" t="s">
+      <c r="K16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1198,13 +1302,19 @@
         <v>13</v>
       </c>
       <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17">
         <v>1.4</v>
       </c>
-      <c r="I17" t="s">
+      <c r="K17" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2</v>
       </c>
@@ -1227,13 +1337,19 @@
         <v>13</v>
       </c>
       <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18">
         <v>0.9</v>
       </c>
-      <c r="I18" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K18" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2</v>
       </c>
@@ -1256,13 +1372,19 @@
         <v>47</v>
       </c>
       <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="I19">
+        <v>6</v>
+      </c>
+      <c r="J19">
         <v>1.6</v>
       </c>
-      <c r="I19" t="s">
+      <c r="K19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2</v>
       </c>
@@ -1285,13 +1407,19 @@
         <v>22</v>
       </c>
       <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
         <v>1.6</v>
       </c>
-      <c r="I20" t="s">
+      <c r="K20" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2</v>
       </c>
@@ -1314,13 +1442,19 @@
         <v>24</v>
       </c>
       <c r="H21">
+        <v>2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
         <v>0.5</v>
       </c>
-      <c r="I21" t="s">
+      <c r="K21" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>3</v>
       </c>
@@ -1343,13 +1477,19 @@
         <v>22</v>
       </c>
       <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
         <v>1.7</v>
       </c>
-      <c r="I22" t="s">
+      <c r="K22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>3</v>
       </c>
@@ -1372,13 +1512,19 @@
         <v>22</v>
       </c>
       <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
         <v>0.9</v>
       </c>
-      <c r="I23" t="s">
+      <c r="K23" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>3</v>
       </c>
@@ -1401,13 +1547,19 @@
         <v>22</v>
       </c>
       <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
         <v>0.7</v>
       </c>
-      <c r="I24" t="s">
+      <c r="K24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -1430,13 +1582,19 @@
         <v>48</v>
       </c>
       <c r="H25">
+        <v>3</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
         <v>1.5</v>
       </c>
-      <c r="I25" t="s">
+      <c r="K25" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>3</v>
       </c>
@@ -1459,13 +1617,19 @@
         <v>28</v>
       </c>
       <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26">
         <v>1.4</v>
       </c>
-      <c r="I26" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>3</v>
       </c>
@@ -1488,13 +1652,19 @@
         <v>49</v>
       </c>
       <c r="H27">
+        <v>2</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27">
         <v>2.4</v>
       </c>
-      <c r="I27" t="s">
+      <c r="K27" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>3</v>
       </c>
@@ -1517,13 +1687,19 @@
         <v>50</v>
       </c>
       <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
         <v>3</v>
       </c>
-      <c r="I28" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J28">
+        <v>3</v>
+      </c>
+      <c r="K28" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>3</v>
       </c>
@@ -1546,13 +1722,19 @@
         <v>32</v>
       </c>
       <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
         <v>1.2</v>
       </c>
-      <c r="I29" t="s">
+      <c r="K29" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>3</v>
       </c>
@@ -1575,13 +1757,19 @@
         <v>22</v>
       </c>
       <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
         <v>0.5</v>
       </c>
-      <c r="I30" t="s">
+      <c r="K30" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>3</v>
       </c>
@@ -1604,13 +1792,19 @@
         <v>19</v>
       </c>
       <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>3</v>
+      </c>
+      <c r="J31">
         <v>1.8</v>
       </c>
-      <c r="I31" t="s">
+      <c r="K31" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>4</v>
       </c>
@@ -1633,13 +1827,19 @@
         <v>19</v>
       </c>
       <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>3</v>
+      </c>
+      <c r="J32">
         <v>2.6</v>
       </c>
-      <c r="I32" t="s">
+      <c r="K32" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>4</v>
       </c>
@@ -1662,13 +1862,19 @@
         <v>32</v>
       </c>
       <c r="H33">
-        <v>1</v>
-      </c>
-      <c r="I33" t="s">
+        <v>2</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>4</v>
       </c>
@@ -1691,13 +1897,19 @@
         <v>45</v>
       </c>
       <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34">
         <v>0.4</v>
       </c>
-      <c r="I34" t="s">
+      <c r="K34" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>4</v>
       </c>
@@ -1720,13 +1932,19 @@
         <v>53</v>
       </c>
       <c r="H35">
+        <v>2</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+      <c r="J35">
         <v>1.2</v>
       </c>
-      <c r="I35" t="s">
+      <c r="K35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>4</v>
       </c>
@@ -1749,13 +1967,19 @@
         <v>22</v>
       </c>
       <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36">
         <v>0.8</v>
       </c>
-      <c r="I36" t="s">
+      <c r="K36" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>4</v>
       </c>
@@ -1778,13 +2002,19 @@
         <v>54</v>
       </c>
       <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
         <v>0.3</v>
       </c>
-      <c r="I37" t="s">
+      <c r="K37" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>4</v>
       </c>
@@ -1807,13 +2037,19 @@
         <v>55</v>
       </c>
       <c r="H38">
+        <v>3</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
+      </c>
+      <c r="J38">
         <v>0.9</v>
       </c>
-      <c r="I38" t="s">
+      <c r="K38" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>4</v>
       </c>
@@ -1836,13 +2072,19 @@
         <v>45</v>
       </c>
       <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39">
         <v>0.8</v>
       </c>
-      <c r="I39" t="s">
+      <c r="K39" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>4</v>
       </c>
@@ -1865,13 +2107,19 @@
         <v>45</v>
       </c>
       <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40">
         <v>0.7</v>
       </c>
-      <c r="I40" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K40" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>4</v>
       </c>
@@ -1894,13 +2142,19 @@
         <v>28</v>
       </c>
       <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>2</v>
+      </c>
+      <c r="J41">
         <v>1.5</v>
       </c>
-      <c r="I41" t="s">
+      <c r="K41" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>5</v>
       </c>
@@ -1923,13 +2177,19 @@
         <v>19</v>
       </c>
       <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>3</v>
+      </c>
+      <c r="J42">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I42" t="s">
+      <c r="K42" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>5</v>
       </c>
@@ -1952,13 +2212,19 @@
         <v>48</v>
       </c>
       <c r="H43">
+        <v>3</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43">
         <v>0.8</v>
       </c>
-      <c r="I43" t="s">
+      <c r="K43" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>5</v>
       </c>
@@ -1981,13 +2247,19 @@
         <v>48</v>
       </c>
       <c r="H44">
+        <v>3</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44">
         <v>0.5</v>
       </c>
-      <c r="I44" t="s">
+      <c r="K44" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>5</v>
       </c>
@@ -2010,13 +2282,19 @@
         <v>48</v>
       </c>
       <c r="H45">
+        <v>3</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45">
         <v>1.5</v>
       </c>
-      <c r="I45" t="s">
+      <c r="K45" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>5</v>
       </c>
@@ -2039,13 +2317,19 @@
         <v>22</v>
       </c>
       <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="J46">
         <v>1.6</v>
       </c>
-      <c r="I46" t="s">
+      <c r="K46" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>5</v>
       </c>
@@ -2068,13 +2352,19 @@
         <v>22</v>
       </c>
       <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I47" t="s">
+      <c r="K47" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>5</v>
       </c>
@@ -2097,13 +2387,19 @@
         <v>56</v>
       </c>
       <c r="H48">
+        <v>3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I48" t="s">
+      <c r="K48" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>5</v>
       </c>
@@ -2126,13 +2422,19 @@
         <v>54</v>
       </c>
       <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
         <v>1.6</v>
       </c>
-      <c r="I49" t="s">
+      <c r="K49" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>5</v>
       </c>
@@ -2155,13 +2457,19 @@
         <v>53</v>
       </c>
       <c r="H50">
+        <v>2</v>
+      </c>
+      <c r="I50">
+        <v>2</v>
+      </c>
+      <c r="J50">
         <v>1.4</v>
       </c>
-      <c r="I50" t="s">
+      <c r="K50" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>5</v>
       </c>
@@ -2184,13 +2492,19 @@
         <v>53</v>
       </c>
       <c r="H51">
+        <v>2</v>
+      </c>
+      <c r="I51">
+        <v>2</v>
+      </c>
+      <c r="J51">
         <v>0.7</v>
       </c>
-      <c r="I51" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K51" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>6</v>
       </c>
@@ -2213,13 +2527,19 @@
         <v>22</v>
       </c>
       <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="J52">
         <v>0.9</v>
       </c>
-      <c r="I52" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K52" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>6</v>
       </c>
@@ -2244,11 +2564,17 @@
       <c r="H53">
         <v>1</v>
       </c>
-      <c r="I53" t="s">
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>6</v>
       </c>
@@ -2271,13 +2597,19 @@
         <v>32</v>
       </c>
       <c r="H54">
+        <v>2</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="J54">
         <v>0.9</v>
       </c>
-      <c r="I54" t="s">
+      <c r="K54" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>6</v>
       </c>
@@ -2300,13 +2632,19 @@
         <v>57</v>
       </c>
       <c r="H55">
+        <v>4</v>
+      </c>
+      <c r="I55">
+        <v>2</v>
+      </c>
+      <c r="J55">
         <v>0.3</v>
       </c>
-      <c r="I55" t="s">
+      <c r="K55" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>6</v>
       </c>
@@ -2329,13 +2667,19 @@
         <v>57</v>
       </c>
       <c r="H56">
+        <v>4</v>
+      </c>
+      <c r="I56">
+        <v>2</v>
+      </c>
+      <c r="J56">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I56" t="s">
+      <c r="K56" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>6</v>
       </c>
@@ -2358,13 +2702,19 @@
         <v>45</v>
       </c>
       <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57">
         <v>1.3</v>
       </c>
-      <c r="I57" t="s">
+      <c r="K57" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>6</v>
       </c>
@@ -2387,13 +2737,19 @@
         <v>28</v>
       </c>
       <c r="H58">
+        <v>1</v>
+      </c>
+      <c r="I58">
+        <v>2</v>
+      </c>
+      <c r="J58">
         <v>2.5</v>
       </c>
-      <c r="I58" t="s">
+      <c r="K58" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>6</v>
       </c>
@@ -2416,13 +2772,19 @@
         <v>53</v>
       </c>
       <c r="H59">
+        <v>2</v>
+      </c>
+      <c r="I59">
+        <v>2</v>
+      </c>
+      <c r="J59">
         <v>0.8</v>
       </c>
-      <c r="I59" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K59" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>6</v>
       </c>
@@ -2445,13 +2807,19 @@
         <v>19</v>
       </c>
       <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>3</v>
+      </c>
+      <c r="J60">
         <v>4.4000000000000004</v>
       </c>
-      <c r="I60" t="s">
+      <c r="K60" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>6</v>
       </c>
@@ -2474,13 +2842,19 @@
         <v>48</v>
       </c>
       <c r="H61">
+        <v>3</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+      <c r="J61">
         <v>0.6</v>
       </c>
-      <c r="I61" t="s">
+      <c r="K61" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>7</v>
       </c>
@@ -2503,13 +2877,19 @@
         <v>45</v>
       </c>
       <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+      <c r="J62">
         <v>1.4</v>
       </c>
-      <c r="I62" t="s">
+      <c r="K62" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>7</v>
       </c>
@@ -2532,13 +2912,19 @@
         <v>58</v>
       </c>
       <c r="H63">
-        <v>1</v>
-      </c>
-      <c r="I63" t="s">
+        <v>5</v>
+      </c>
+      <c r="I63">
+        <v>3</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+      <c r="K63" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>7</v>
       </c>
@@ -2561,13 +2947,19 @@
         <v>8</v>
       </c>
       <c r="H64">
+        <v>1</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
         <v>2.1</v>
       </c>
-      <c r="I64" t="s">
+      <c r="K64" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>7</v>
       </c>
@@ -2590,13 +2982,19 @@
         <v>55</v>
       </c>
       <c r="H65">
+        <v>3</v>
+      </c>
+      <c r="I65">
+        <v>2</v>
+      </c>
+      <c r="J65">
         <v>2.6</v>
       </c>
-      <c r="I65" t="s">
+      <c r="K65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>7</v>
       </c>
@@ -2619,13 +3017,19 @@
         <v>44</v>
       </c>
       <c r="H66">
+        <v>4</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+      <c r="J66">
         <v>0.6</v>
       </c>
-      <c r="I66" t="s">
+      <c r="K66" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>7</v>
       </c>
@@ -2648,13 +3052,19 @@
         <v>48</v>
       </c>
       <c r="H67">
+        <v>3</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+      <c r="J67">
         <v>0.6</v>
       </c>
-      <c r="I67" t="s">
+      <c r="K67" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>7</v>
       </c>
@@ -2677,13 +3087,19 @@
         <v>54</v>
       </c>
       <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
         <v>2.1</v>
       </c>
-      <c r="I68" t="s">
+      <c r="K68" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>7</v>
       </c>
@@ -2706,13 +3122,19 @@
         <v>54</v>
       </c>
       <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
         <v>0.6</v>
       </c>
-      <c r="I69" t="s">
+      <c r="K69" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>7</v>
       </c>
@@ -2735,13 +3157,19 @@
         <v>22</v>
       </c>
       <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+      <c r="J70">
         <v>0.9</v>
       </c>
-      <c r="I70" t="s">
+      <c r="K70" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>7</v>
       </c>
@@ -2764,13 +3192,19 @@
         <v>55</v>
       </c>
       <c r="H71">
+        <v>3</v>
+      </c>
+      <c r="I71">
+        <v>2</v>
+      </c>
+      <c r="J71">
         <v>1.3</v>
       </c>
-      <c r="I71" t="s">
+      <c r="K71" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>8</v>
       </c>
@@ -2793,13 +3227,19 @@
         <v>44</v>
       </c>
       <c r="H72">
+        <v>4</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72">
         <v>0.8</v>
       </c>
-      <c r="I72" t="s">
+      <c r="K72" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>8</v>
       </c>
@@ -2822,13 +3262,19 @@
         <v>50</v>
       </c>
       <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73">
+        <v>3</v>
+      </c>
+      <c r="J73">
         <v>1.6</v>
       </c>
-      <c r="I73" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K73" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>8</v>
       </c>
@@ -2851,13 +3297,19 @@
         <v>13</v>
       </c>
       <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>2</v>
+      </c>
+      <c r="J74">
         <v>1.7</v>
       </c>
-      <c r="I74" t="s">
+      <c r="K74" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>8</v>
       </c>
@@ -2880,13 +3332,19 @@
         <v>49</v>
       </c>
       <c r="H75">
+        <v>2</v>
+      </c>
+      <c r="I75">
+        <v>3</v>
+      </c>
+      <c r="J75">
         <v>3.1</v>
       </c>
-      <c r="I75" t="s">
+      <c r="K75" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>8</v>
       </c>
@@ -2909,13 +3367,19 @@
         <v>32</v>
       </c>
       <c r="H76">
+        <v>2</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+      <c r="J76">
         <v>0.9</v>
       </c>
-      <c r="I76" t="s">
+      <c r="K76" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>8</v>
       </c>
@@ -2938,13 +3402,19 @@
         <v>45</v>
       </c>
       <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I77" t="s">
+      <c r="K77" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>8</v>
       </c>
@@ -2967,13 +3437,19 @@
         <v>24</v>
       </c>
       <c r="H78">
+        <v>2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
         <v>0.7</v>
       </c>
-      <c r="I78" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K78" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>8</v>
       </c>
@@ -2996,13 +3472,19 @@
         <v>28</v>
       </c>
       <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79">
+        <v>2</v>
+      </c>
+      <c r="J79">
         <v>1.6</v>
       </c>
-      <c r="I79" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K79" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>8</v>
       </c>
@@ -3025,13 +3507,19 @@
         <v>32</v>
       </c>
       <c r="H80">
-        <v>1</v>
-      </c>
-      <c r="I80" t="s">
+        <v>2</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+      <c r="J80">
+        <v>1</v>
+      </c>
+      <c r="K80" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>8</v>
       </c>
@@ -3056,11 +3544,17 @@
       <c r="H81">
         <v>1</v>
       </c>
-      <c r="I81" t="s">
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>9</v>
       </c>
@@ -3083,13 +3577,19 @@
         <v>50</v>
       </c>
       <c r="H82">
+        <v>1</v>
+      </c>
+      <c r="I82">
+        <v>3</v>
+      </c>
+      <c r="J82">
         <v>1.7</v>
       </c>
-      <c r="I82" t="s">
+      <c r="K82" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>9</v>
       </c>
@@ -3112,13 +3612,19 @@
         <v>53</v>
       </c>
       <c r="H83">
+        <v>2</v>
+      </c>
+      <c r="I83">
+        <v>2</v>
+      </c>
+      <c r="J83">
         <v>1.3</v>
       </c>
-      <c r="I83" t="s">
+      <c r="K83" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>9</v>
       </c>
@@ -3141,13 +3647,19 @@
         <v>8</v>
       </c>
       <c r="H84">
+        <v>1</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
         <v>0.2</v>
       </c>
-      <c r="I84" t="s">
+      <c r="K84" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>9</v>
       </c>
@@ -3170,13 +3682,19 @@
         <v>59</v>
       </c>
       <c r="H85">
+        <v>4</v>
+      </c>
+      <c r="I85">
+        <v>3</v>
+      </c>
+      <c r="J85">
         <v>1.3</v>
       </c>
-      <c r="I85" t="s">
+      <c r="K85" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>9</v>
       </c>
@@ -3199,13 +3717,19 @@
         <v>22</v>
       </c>
       <c r="H86">
+        <v>1</v>
+      </c>
+      <c r="I86">
+        <v>1</v>
+      </c>
+      <c r="J86">
         <v>0.3</v>
       </c>
-      <c r="I86" t="s">
+      <c r="K86" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>9</v>
       </c>
@@ -3228,13 +3752,19 @@
         <v>22</v>
       </c>
       <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="J87">
         <v>1.2</v>
       </c>
-      <c r="I87" t="s">
+      <c r="K87" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>9</v>
       </c>
@@ -3257,13 +3787,19 @@
         <v>32</v>
       </c>
       <c r="H88">
+        <v>2</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+      <c r="J88">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I88" t="s">
+      <c r="K88" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>9</v>
       </c>
@@ -3286,13 +3822,19 @@
         <v>32</v>
       </c>
       <c r="H89">
+        <v>2</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="J89">
         <v>1.8</v>
       </c>
-      <c r="I89" t="s">
+      <c r="K89" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>9</v>
       </c>
@@ -3315,13 +3857,19 @@
         <v>8</v>
       </c>
       <c r="H90">
+        <v>1</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
         <v>0.7</v>
       </c>
-      <c r="I90" t="s">
+      <c r="K90" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>9</v>
       </c>
@@ -3344,13 +3892,19 @@
         <v>53</v>
       </c>
       <c r="H91">
+        <v>2</v>
+      </c>
+      <c r="I91">
+        <v>2</v>
+      </c>
+      <c r="J91">
         <v>0.8</v>
       </c>
-      <c r="I91" t="s">
+      <c r="K91" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>10</v>
       </c>
@@ -3373,13 +3927,19 @@
         <v>8</v>
       </c>
       <c r="H92">
+        <v>1</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I92" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K92" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>10</v>
       </c>
@@ -3402,13 +3962,19 @@
         <v>32</v>
       </c>
       <c r="H93">
-        <v>1</v>
-      </c>
-      <c r="I93" t="s">
+        <v>2</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="J93">
+        <v>1</v>
+      </c>
+      <c r="K93" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>10</v>
       </c>
@@ -3431,13 +3997,19 @@
         <v>8</v>
       </c>
       <c r="H94">
+        <v>1</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
         <v>1.6</v>
       </c>
-      <c r="I94" t="s">
+      <c r="K94" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>10</v>
       </c>
@@ -3460,13 +4032,19 @@
         <v>56</v>
       </c>
       <c r="H95">
+        <v>3</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
         <v>0.1</v>
       </c>
-      <c r="I95" t="s">
+      <c r="K95" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>10</v>
       </c>
@@ -3489,13 +4067,19 @@
         <v>22</v>
       </c>
       <c r="H96">
+        <v>1</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96">
         <v>1.5</v>
       </c>
-      <c r="I96" t="s">
+      <c r="K96" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>10</v>
       </c>
@@ -3518,13 +4102,19 @@
         <v>32</v>
       </c>
       <c r="H97">
+        <v>2</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97">
         <v>1.6</v>
       </c>
-      <c r="I97" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K97" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>10</v>
       </c>
@@ -3547,13 +4137,19 @@
         <v>53</v>
       </c>
       <c r="H98">
+        <v>2</v>
+      </c>
+      <c r="I98">
+        <v>2</v>
+      </c>
+      <c r="J98">
         <v>2.4</v>
       </c>
-      <c r="I98" t="s">
+      <c r="K98" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>10</v>
       </c>
@@ -3576,13 +4172,19 @@
         <v>44</v>
       </c>
       <c r="H99">
+        <v>4</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99">
         <v>1.8</v>
       </c>
-      <c r="I99" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K99" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>10</v>
       </c>
@@ -3605,13 +4207,19 @@
         <v>22</v>
       </c>
       <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="J100">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I100" t="s">
+      <c r="K100" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>10</v>
       </c>
@@ -3634,13 +4242,19 @@
         <v>32</v>
       </c>
       <c r="H101">
+        <v>2</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101">
         <v>0.6</v>
       </c>
-      <c r="I101" t="s">
+      <c r="K101" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>11</v>
       </c>
@@ -3663,13 +4277,19 @@
         <v>54</v>
       </c>
       <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I102" t="s">
+      <c r="K102" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>11</v>
       </c>
@@ -3692,13 +4312,19 @@
         <v>13</v>
       </c>
       <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>2</v>
+      </c>
+      <c r="J103">
         <v>1.8</v>
       </c>
-      <c r="I103" t="s">
+      <c r="K103" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>11</v>
       </c>
@@ -3721,13 +4347,19 @@
         <v>24</v>
       </c>
       <c r="H104">
+        <v>2</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
         <v>0.6</v>
       </c>
-      <c r="I104" t="s">
+      <c r="K104" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>11</v>
       </c>
@@ -3750,13 +4382,19 @@
         <v>55</v>
       </c>
       <c r="H105">
+        <v>3</v>
+      </c>
+      <c r="I105">
+        <v>2</v>
+      </c>
+      <c r="J105">
         <v>2.6</v>
       </c>
-      <c r="I105" t="s">
+      <c r="K105" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>11</v>
       </c>
@@ -3779,13 +4417,19 @@
         <v>32</v>
       </c>
       <c r="H106">
+        <v>2</v>
+      </c>
+      <c r="I106">
+        <v>1</v>
+      </c>
+      <c r="J106">
         <v>2.1</v>
       </c>
-      <c r="I106" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K106" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>11</v>
       </c>
@@ -3808,13 +4452,19 @@
         <v>24</v>
       </c>
       <c r="H107">
+        <v>2</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
         <v>1.2</v>
       </c>
-      <c r="I107" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K107" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>11</v>
       </c>
@@ -3837,13 +4487,19 @@
         <v>28</v>
       </c>
       <c r="H108">
+        <v>1</v>
+      </c>
+      <c r="I108">
+        <v>2</v>
+      </c>
+      <c r="J108">
         <v>1.6</v>
       </c>
-      <c r="I108" t="s">
+      <c r="K108" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>11</v>
       </c>
@@ -3866,13 +4522,19 @@
         <v>50</v>
       </c>
       <c r="H109">
+        <v>1</v>
+      </c>
+      <c r="I109">
+        <v>3</v>
+      </c>
+      <c r="J109">
         <v>1.6</v>
       </c>
-      <c r="I109" t="s">
+      <c r="K109" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>11</v>
       </c>
@@ -3895,13 +4557,19 @@
         <v>56</v>
       </c>
       <c r="H110">
+        <v>3</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
         <v>0.6</v>
       </c>
-      <c r="I110" t="s">
+      <c r="K110" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>11</v>
       </c>
@@ -3924,13 +4592,19 @@
         <v>22</v>
       </c>
       <c r="H111">
+        <v>1</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+      <c r="J111">
         <v>1.5</v>
       </c>
-      <c r="I111" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K111" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>12</v>
       </c>
@@ -3953,13 +4627,19 @@
         <v>28</v>
       </c>
       <c r="H112">
+        <v>1</v>
+      </c>
+      <c r="I112">
+        <v>2</v>
+      </c>
+      <c r="J112">
         <v>2.7</v>
       </c>
-      <c r="I112" t="s">
+      <c r="K112" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>12</v>
       </c>
@@ -3982,13 +4662,19 @@
         <v>53</v>
       </c>
       <c r="H113">
+        <v>2</v>
+      </c>
+      <c r="I113">
+        <v>2</v>
+      </c>
+      <c r="J113">
         <v>1.3</v>
       </c>
-      <c r="I113" t="s">
+      <c r="K113" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>12</v>
       </c>
@@ -4011,13 +4697,19 @@
         <v>60</v>
       </c>
       <c r="H114">
+        <v>1</v>
+      </c>
+      <c r="I114">
+        <v>4</v>
+      </c>
+      <c r="J114">
         <v>1.3</v>
       </c>
-      <c r="I114" t="s">
+      <c r="K114" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>12</v>
       </c>
@@ -4040,13 +4732,19 @@
         <v>28</v>
       </c>
       <c r="H115">
+        <v>1</v>
+      </c>
+      <c r="I115">
+        <v>2</v>
+      </c>
+      <c r="J115">
         <v>0.9</v>
       </c>
-      <c r="I115" t="s">
+      <c r="K115" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>12</v>
       </c>
@@ -4069,13 +4767,19 @@
         <v>56</v>
       </c>
       <c r="H116">
+        <v>3</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
         <v>0.3</v>
       </c>
-      <c r="I116" t="s">
+      <c r="K116" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>12</v>
       </c>
@@ -4098,13 +4802,19 @@
         <v>54</v>
       </c>
       <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I117" t="s">
+      <c r="K117" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>12</v>
       </c>
@@ -4127,13 +4837,19 @@
         <v>61</v>
       </c>
       <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>4</v>
+      </c>
+      <c r="J118">
         <v>2.5</v>
       </c>
-      <c r="I118" t="s">
+      <c r="K118" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>12</v>
       </c>
@@ -4156,13 +4872,19 @@
         <v>49</v>
       </c>
       <c r="H119">
+        <v>2</v>
+      </c>
+      <c r="I119">
+        <v>3</v>
+      </c>
+      <c r="J119">
         <v>3.1</v>
       </c>
-      <c r="I119" t="s">
+      <c r="K119" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>12</v>
       </c>
@@ -4185,13 +4907,19 @@
         <v>22</v>
       </c>
       <c r="H120">
+        <v>1</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
+      </c>
+      <c r="J120">
         <v>0.8</v>
       </c>
-      <c r="I120" t="s">
+      <c r="K120" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>12</v>
       </c>
@@ -4214,13 +4942,19 @@
         <v>13</v>
       </c>
       <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <v>2</v>
+      </c>
+      <c r="J121">
         <v>0.9</v>
       </c>
-      <c r="I121" t="s">
+      <c r="K121" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>13</v>
       </c>
@@ -4245,11 +4979,17 @@
       <c r="H122">
         <v>1</v>
       </c>
-      <c r="I122" t="s">
+      <c r="I122">
+        <v>1</v>
+      </c>
+      <c r="J122">
+        <v>1</v>
+      </c>
+      <c r="K122" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>13</v>
       </c>
@@ -4272,13 +5012,19 @@
         <v>62</v>
       </c>
       <c r="H123">
+        <v>2</v>
+      </c>
+      <c r="I123">
+        <v>4</v>
+      </c>
+      <c r="J123">
         <v>3.3</v>
       </c>
-      <c r="I123" t="s">
+      <c r="K123" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>13</v>
       </c>
@@ -4301,13 +5047,19 @@
         <v>8</v>
       </c>
       <c r="H124">
+        <v>1</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
         <v>0.6</v>
       </c>
-      <c r="I124" t="s">
+      <c r="K124" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>13</v>
       </c>
@@ -4330,13 +5082,19 @@
         <v>44</v>
       </c>
       <c r="H125">
+        <v>4</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="J125">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I125" t="s">
+      <c r="K125" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>13</v>
       </c>
@@ -4359,13 +5117,19 @@
         <v>22</v>
       </c>
       <c r="H126">
-        <v>0</v>
-      </c>
-      <c r="I126" t="s">
+        <v>1</v>
+      </c>
+      <c r="I126">
+        <v>1</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>13</v>
       </c>
@@ -4388,13 +5152,19 @@
         <v>63</v>
       </c>
       <c r="H127">
+        <v>2</v>
+      </c>
+      <c r="I127">
+        <v>5</v>
+      </c>
+      <c r="J127">
         <v>3.5</v>
       </c>
-      <c r="I127" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K127" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>13</v>
       </c>
@@ -4417,13 +5187,19 @@
         <v>46</v>
       </c>
       <c r="H128">
+        <v>4</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
         <v>0.6</v>
       </c>
-      <c r="I128" t="s">
+      <c r="K128" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>13</v>
       </c>
@@ -4446,13 +5222,19 @@
         <v>22</v>
       </c>
       <c r="H129">
+        <v>1</v>
+      </c>
+      <c r="I129">
+        <v>1</v>
+      </c>
+      <c r="J129">
         <v>1.5</v>
       </c>
-      <c r="I129" t="s">
+      <c r="K129" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>13</v>
       </c>
@@ -4475,13 +5257,19 @@
         <v>56</v>
       </c>
       <c r="H130">
+        <v>3</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
         <v>1.2</v>
       </c>
-      <c r="I130" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K130" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>13</v>
       </c>
@@ -4504,13 +5292,19 @@
         <v>24</v>
       </c>
       <c r="H131">
+        <v>2</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
         <v>0.8</v>
       </c>
-      <c r="I131" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K131" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>14</v>
       </c>
@@ -4533,13 +5327,19 @@
         <v>45</v>
       </c>
       <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+      <c r="J132">
         <v>1.6</v>
       </c>
-      <c r="I132" t="s">
+      <c r="K132" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>14</v>
       </c>
@@ -4564,11 +5364,17 @@
       <c r="H133">
         <v>3</v>
       </c>
-      <c r="I133" t="s">
+      <c r="I133">
+        <v>1</v>
+      </c>
+      <c r="J133">
+        <v>3</v>
+      </c>
+      <c r="K133" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>14</v>
       </c>
@@ -4591,13 +5397,19 @@
         <v>68</v>
       </c>
       <c r="H134">
+        <v>3</v>
+      </c>
+      <c r="I134">
+        <v>3</v>
+      </c>
+      <c r="J134">
         <v>1.9</v>
       </c>
-      <c r="I134" t="s">
+      <c r="K134" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>14</v>
       </c>
@@ -4620,13 +5432,19 @@
         <v>46</v>
       </c>
       <c r="H135">
+        <v>4</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
         <v>0.8</v>
       </c>
-      <c r="I135" t="s">
+      <c r="K135" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>14</v>
       </c>
@@ -4649,13 +5467,19 @@
         <v>56</v>
       </c>
       <c r="H136">
-        <v>1</v>
-      </c>
-      <c r="I136" t="s">
+        <v>3</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>1</v>
+      </c>
+      <c r="K136" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>14</v>
       </c>
@@ -4678,13 +5502,19 @@
         <v>69</v>
       </c>
       <c r="H137">
+        <v>1</v>
+      </c>
+      <c r="I137">
+        <v>5</v>
+      </c>
+      <c r="J137">
         <v>5.2</v>
       </c>
-      <c r="I137" t="s">
+      <c r="K137" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>14</v>
       </c>
@@ -4707,13 +5537,19 @@
         <v>24</v>
       </c>
       <c r="H138">
+        <v>2</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
         <v>0.2</v>
       </c>
-      <c r="I138" t="s">
+      <c r="K138" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>14</v>
       </c>
@@ -4736,13 +5572,19 @@
         <v>48</v>
       </c>
       <c r="H139">
+        <v>3</v>
+      </c>
+      <c r="I139">
+        <v>1</v>
+      </c>
+      <c r="J139">
         <v>0.9</v>
       </c>
-      <c r="I139" t="s">
+      <c r="K139" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>14</v>
       </c>
@@ -4765,13 +5607,19 @@
         <v>48</v>
       </c>
       <c r="H140">
+        <v>3</v>
+      </c>
+      <c r="I140">
+        <v>1</v>
+      </c>
+      <c r="J140">
         <v>1.4</v>
       </c>
-      <c r="I140" t="s">
+      <c r="K140" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>14</v>
       </c>
@@ -4794,13 +5642,19 @@
         <v>8</v>
       </c>
       <c r="H141">
+        <v>1</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
         <v>0.9</v>
       </c>
-      <c r="I141" t="s">
+      <c r="K141" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>15</v>
       </c>
@@ -4823,13 +5677,19 @@
         <v>8</v>
       </c>
       <c r="H142">
+        <v>1</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
         <v>0.3</v>
       </c>
-      <c r="I142" t="s">
+      <c r="K142" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>15</v>
       </c>
@@ -4852,13 +5712,19 @@
         <v>53</v>
       </c>
       <c r="H143">
+        <v>2</v>
+      </c>
+      <c r="I143">
+        <v>2</v>
+      </c>
+      <c r="J143">
         <v>1.4</v>
       </c>
-      <c r="I143" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K143" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>15</v>
       </c>
@@ -4881,13 +5747,19 @@
         <v>57</v>
       </c>
       <c r="H144">
+        <v>4</v>
+      </c>
+      <c r="I144">
+        <v>2</v>
+      </c>
+      <c r="J144">
         <v>1.5</v>
       </c>
-      <c r="I144" t="s">
+      <c r="K144" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>15</v>
       </c>
@@ -4910,13 +5782,19 @@
         <v>49</v>
       </c>
       <c r="H145">
+        <v>2</v>
+      </c>
+      <c r="I145">
+        <v>3</v>
+      </c>
+      <c r="J145">
         <v>0.8</v>
       </c>
-      <c r="I145" t="s">
+      <c r="K145" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>15</v>
       </c>
@@ -4939,13 +5817,19 @@
         <v>53</v>
       </c>
       <c r="H146">
+        <v>2</v>
+      </c>
+      <c r="I146">
+        <v>2</v>
+      </c>
+      <c r="J146">
         <v>1.5</v>
       </c>
-      <c r="I146" t="s">
+      <c r="K146" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>15</v>
       </c>
@@ -4968,13 +5852,19 @@
         <v>28</v>
       </c>
       <c r="H147">
+        <v>1</v>
+      </c>
+      <c r="I147">
+        <v>2</v>
+      </c>
+      <c r="J147">
         <v>3.2</v>
       </c>
-      <c r="I147" t="s">
+      <c r="K147" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>15</v>
       </c>
@@ -4997,13 +5887,19 @@
         <v>22</v>
       </c>
       <c r="H148">
+        <v>1</v>
+      </c>
+      <c r="I148">
+        <v>1</v>
+      </c>
+      <c r="J148">
         <v>1.8</v>
       </c>
-      <c r="I148" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K148" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>15</v>
       </c>
@@ -5026,13 +5922,19 @@
         <v>71</v>
       </c>
       <c r="H149">
+        <v>3</v>
+      </c>
+      <c r="I149">
+        <v>4</v>
+      </c>
+      <c r="J149">
         <v>2.8</v>
       </c>
-      <c r="I149" t="s">
+      <c r="K149" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>15</v>
       </c>
@@ -5055,13 +5957,19 @@
         <v>32</v>
       </c>
       <c r="H150">
+        <v>2</v>
+      </c>
+      <c r="I150">
+        <v>1</v>
+      </c>
+      <c r="J150">
         <v>1.4</v>
       </c>
-      <c r="I150" t="s">
+      <c r="K150" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>16</v>
       </c>
@@ -5084,13 +5992,19 @@
         <v>53</v>
       </c>
       <c r="H151">
+        <v>2</v>
+      </c>
+      <c r="I151">
+        <v>2</v>
+      </c>
+      <c r="J151">
         <v>1.2</v>
       </c>
-      <c r="I151" t="s">
+      <c r="K151" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>16</v>
       </c>
@@ -5113,13 +6027,19 @@
         <v>28</v>
       </c>
       <c r="H152">
+        <v>1</v>
+      </c>
+      <c r="I152">
+        <v>2</v>
+      </c>
+      <c r="J152">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I152" t="s">
+      <c r="K152" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>16</v>
       </c>
@@ -5142,13 +6062,19 @@
         <v>46</v>
       </c>
       <c r="H153">
+        <v>4</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="J153">
         <v>0.2</v>
       </c>
-      <c r="I153" t="s">
+      <c r="K153" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>16</v>
       </c>
@@ -5171,13 +6097,19 @@
         <v>54</v>
       </c>
       <c r="H154">
+        <v>0</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
         <v>0.1</v>
       </c>
-      <c r="I154" t="s">
+      <c r="K154" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>16</v>
       </c>
@@ -5200,13 +6132,19 @@
         <v>32</v>
       </c>
       <c r="H155">
+        <v>2</v>
+      </c>
+      <c r="I155">
+        <v>1</v>
+      </c>
+      <c r="J155">
         <v>0.4</v>
       </c>
-      <c r="I155" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K155" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>16</v>
       </c>
@@ -5229,13 +6167,19 @@
         <v>50</v>
       </c>
       <c r="H156">
+        <v>1</v>
+      </c>
+      <c r="I156">
+        <v>3</v>
+      </c>
+      <c r="J156">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I156" t="s">
+      <c r="K156" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>16</v>
       </c>
@@ -5258,13 +6202,19 @@
         <v>28</v>
       </c>
       <c r="H157">
+        <v>1</v>
+      </c>
+      <c r="I157">
+        <v>2</v>
+      </c>
+      <c r="J157">
         <v>2.1</v>
       </c>
-      <c r="I157" t="s">
+      <c r="K157" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>16</v>
       </c>
@@ -5287,13 +6237,19 @@
         <v>73</v>
       </c>
       <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158">
+        <v>5</v>
+      </c>
+      <c r="J158">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I158" t="s">
+      <c r="K158" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>16</v>
       </c>
@@ -5316,13 +6272,19 @@
         <v>32</v>
       </c>
       <c r="H159">
+        <v>2</v>
+      </c>
+      <c r="I159">
+        <v>1</v>
+      </c>
+      <c r="J159">
         <v>1.6</v>
       </c>
-      <c r="I159" t="s">
+      <c r="K159" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>16</v>
       </c>
@@ -5345,13 +6307,19 @@
         <v>22</v>
       </c>
       <c r="H160">
+        <v>1</v>
+      </c>
+      <c r="I160">
+        <v>1</v>
+      </c>
+      <c r="J160">
         <v>2.1</v>
       </c>
-      <c r="I160" t="s">
+      <c r="K160" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>17</v>
       </c>
@@ -5374,13 +6342,19 @@
         <v>32</v>
       </c>
       <c r="H161">
-        <v>1</v>
-      </c>
-      <c r="I161" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="I161">
+        <v>1</v>
+      </c>
+      <c r="J161">
+        <v>1</v>
+      </c>
+      <c r="K161" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>17</v>
       </c>
@@ -5403,13 +6377,19 @@
         <v>61</v>
       </c>
       <c r="H162">
+        <v>0</v>
+      </c>
+      <c r="I162">
+        <v>4</v>
+      </c>
+      <c r="J162">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I162" t="s">
+      <c r="K162" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>17</v>
       </c>
@@ -5432,13 +6412,19 @@
         <v>13</v>
       </c>
       <c r="H163">
+        <v>0</v>
+      </c>
+      <c r="I163">
+        <v>2</v>
+      </c>
+      <c r="J163">
         <v>0.9</v>
       </c>
-      <c r="I163" t="s">
+      <c r="K163" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>17</v>
       </c>
@@ -5461,13 +6447,19 @@
         <v>22</v>
       </c>
       <c r="H164">
+        <v>1</v>
+      </c>
+      <c r="I164">
+        <v>1</v>
+      </c>
+      <c r="J164">
         <v>0.9</v>
       </c>
-      <c r="I164" t="s">
+      <c r="K164" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>17</v>
       </c>
@@ -5490,13 +6482,19 @@
         <v>69</v>
       </c>
       <c r="H165">
+        <v>1</v>
+      </c>
+      <c r="I165">
+        <v>5</v>
+      </c>
+      <c r="J165">
         <v>2.5</v>
       </c>
-      <c r="I165" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K165" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>17</v>
       </c>
@@ -5519,13 +6517,19 @@
         <v>19</v>
       </c>
       <c r="H166">
+        <v>0</v>
+      </c>
+      <c r="I166">
+        <v>3</v>
+      </c>
+      <c r="J166">
         <v>1.6</v>
       </c>
-      <c r="I166" t="s">
+      <c r="K166" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>17</v>
       </c>
@@ -5548,13 +6552,19 @@
         <v>19</v>
       </c>
       <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167">
+        <v>3</v>
+      </c>
+      <c r="J167">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I167" t="s">
+      <c r="K167" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>17</v>
       </c>
@@ -5577,13 +6587,19 @@
         <v>54</v>
       </c>
       <c r="H168">
+        <v>0</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
         <v>1.2</v>
       </c>
-      <c r="I168" t="s">
+      <c r="K168" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>17</v>
       </c>
@@ -5606,13 +6622,19 @@
         <v>54</v>
       </c>
       <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="J169">
         <v>0.3</v>
       </c>
-      <c r="I169" t="s">
+      <c r="K169" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>17</v>
       </c>
@@ -5635,13 +6657,19 @@
         <v>74</v>
       </c>
       <c r="H170">
+        <v>3</v>
+      </c>
+      <c r="I170">
+        <v>6</v>
+      </c>
+      <c r="J170">
         <v>5.6</v>
       </c>
-      <c r="I170" t="s">
+      <c r="K170" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>18</v>
       </c>
@@ -5664,13 +6692,19 @@
         <v>22</v>
       </c>
       <c r="H171">
+        <v>1</v>
+      </c>
+      <c r="I171">
+        <v>1</v>
+      </c>
+      <c r="J171">
         <v>0.7</v>
       </c>
-      <c r="I171" t="s">
+      <c r="K171" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>18</v>
       </c>
@@ -5693,13 +6727,19 @@
         <v>45</v>
       </c>
       <c r="H172">
+        <v>0</v>
+      </c>
+      <c r="I172">
+        <v>1</v>
+      </c>
+      <c r="J172">
         <v>1.7</v>
       </c>
-      <c r="I172" t="s">
+      <c r="K172" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>18</v>
       </c>
@@ -5722,13 +6762,19 @@
         <v>56</v>
       </c>
       <c r="H173">
+        <v>3</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
         <v>0.3</v>
       </c>
-      <c r="I173" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K173" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>18</v>
       </c>
@@ -5751,13 +6797,19 @@
         <v>8</v>
       </c>
       <c r="H174">
+        <v>1</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
         <v>0.9</v>
       </c>
-      <c r="I174" t="s">
+      <c r="K174" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>18</v>
       </c>
@@ -5780,13 +6832,19 @@
         <v>54</v>
       </c>
       <c r="H175">
+        <v>0</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
         <v>0.4</v>
       </c>
-      <c r="I175" t="s">
+      <c r="K175" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>18</v>
       </c>
@@ -5809,13 +6867,19 @@
         <v>28</v>
       </c>
       <c r="H176">
+        <v>1</v>
+      </c>
+      <c r="I176">
+        <v>2</v>
+      </c>
+      <c r="J176">
         <v>1.8</v>
       </c>
-      <c r="I176" t="s">
+      <c r="K176" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>18</v>
       </c>
@@ -5838,13 +6902,19 @@
         <v>24</v>
       </c>
       <c r="H177">
+        <v>2</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+      <c r="J177">
         <v>0.4</v>
       </c>
-      <c r="I177" t="s">
+      <c r="K177" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>18</v>
       </c>
@@ -5867,13 +6937,19 @@
         <v>48</v>
       </c>
       <c r="H178">
+        <v>3</v>
+      </c>
+      <c r="I178">
+        <v>1</v>
+      </c>
+      <c r="J178">
         <v>0.3</v>
       </c>
-      <c r="I178" t="s">
+      <c r="K178" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>18</v>
       </c>
@@ -5896,13 +6972,19 @@
         <v>54</v>
       </c>
       <c r="H179">
+        <v>0</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I179" t="s">
+      <c r="K179" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>18</v>
       </c>
@@ -5925,13 +7007,19 @@
         <v>8</v>
       </c>
       <c r="H180">
+        <v>1</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
         <v>0.2</v>
       </c>
-      <c r="I180" t="s">
+      <c r="K180" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>19</v>
       </c>
@@ -5954,13 +7042,19 @@
         <v>13</v>
       </c>
       <c r="H181">
+        <v>0</v>
+      </c>
+      <c r="I181">
+        <v>2</v>
+      </c>
+      <c r="J181">
         <v>1.3</v>
       </c>
-      <c r="I181" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K181" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>19</v>
       </c>
@@ -5983,13 +7077,19 @@
         <v>13</v>
       </c>
       <c r="H182">
+        <v>0</v>
+      </c>
+      <c r="I182">
+        <v>2</v>
+      </c>
+      <c r="J182">
         <v>1.5</v>
       </c>
-      <c r="I182" t="s">
+      <c r="K182" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>19</v>
       </c>
@@ -6012,13 +7112,19 @@
         <v>53</v>
       </c>
       <c r="H183">
+        <v>2</v>
+      </c>
+      <c r="I183">
+        <v>2</v>
+      </c>
+      <c r="J183">
         <v>0.7</v>
       </c>
-      <c r="I183" t="s">
+      <c r="K183" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>19</v>
       </c>
@@ -6043,11 +7149,17 @@
       <c r="H184">
         <v>2</v>
       </c>
-      <c r="I184" t="s">
+      <c r="I184">
+        <v>2</v>
+      </c>
+      <c r="J184">
+        <v>2</v>
+      </c>
+      <c r="K184" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>19</v>
       </c>
@@ -6070,13 +7182,19 @@
         <v>32</v>
       </c>
       <c r="H185">
+        <v>2</v>
+      </c>
+      <c r="I185">
+        <v>1</v>
+      </c>
+      <c r="J185">
         <v>0.9</v>
       </c>
-      <c r="I185" t="s">
+      <c r="K185" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>19</v>
       </c>
@@ -6099,13 +7217,19 @@
         <v>73</v>
       </c>
       <c r="H186">
+        <v>0</v>
+      </c>
+      <c r="I186">
+        <v>5</v>
+      </c>
+      <c r="J186">
         <v>3.1</v>
       </c>
-      <c r="I186" t="s">
+      <c r="K186" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>19</v>
       </c>
@@ -6128,13 +7252,19 @@
         <v>53</v>
       </c>
       <c r="H187">
+        <v>2</v>
+      </c>
+      <c r="I187">
+        <v>2</v>
+      </c>
+      <c r="J187">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I187" t="s">
+      <c r="K187" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>19</v>
       </c>
@@ -6159,11 +7289,17 @@
       <c r="H188">
         <v>2</v>
       </c>
-      <c r="I188" t="s">
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="J188">
+        <v>2</v>
+      </c>
+      <c r="K188" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>19</v>
       </c>
@@ -6186,13 +7322,19 @@
         <v>13</v>
       </c>
       <c r="H189">
+        <v>0</v>
+      </c>
+      <c r="I189">
+        <v>2</v>
+      </c>
+      <c r="J189">
         <v>1.9</v>
       </c>
-      <c r="I189" t="s">
+      <c r="K189" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>19</v>
       </c>
@@ -6215,13 +7357,19 @@
         <v>50</v>
       </c>
       <c r="H190">
+        <v>1</v>
+      </c>
+      <c r="I190">
+        <v>3</v>
+      </c>
+      <c r="J190">
         <v>1.9</v>
       </c>
-      <c r="I190" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K190" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>20</v>
       </c>
@@ -6244,13 +7392,19 @@
         <v>28</v>
       </c>
       <c r="H191">
+        <v>1</v>
+      </c>
+      <c r="I191">
+        <v>2</v>
+      </c>
+      <c r="J191">
         <v>2.5</v>
       </c>
-      <c r="I191" t="s">
+      <c r="K191" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>20</v>
       </c>
@@ -6273,13 +7427,19 @@
         <v>32</v>
       </c>
       <c r="H192">
+        <v>2</v>
+      </c>
+      <c r="I192">
+        <v>1</v>
+      </c>
+      <c r="J192">
         <v>0.4</v>
       </c>
-      <c r="I192" t="s">
+      <c r="K192" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>20</v>
       </c>
@@ -6302,13 +7462,19 @@
         <v>8</v>
       </c>
       <c r="H193">
+        <v>1</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+      <c r="J193">
         <v>0.7</v>
       </c>
-      <c r="I193" t="s">
+      <c r="K193" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>20</v>
       </c>
@@ -6331,13 +7497,19 @@
         <v>22</v>
       </c>
       <c r="H194">
+        <v>1</v>
+      </c>
+      <c r="I194">
+        <v>1</v>
+      </c>
+      <c r="J194">
         <v>1.2</v>
       </c>
-      <c r="I194" t="s">
+      <c r="K194" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>20</v>
       </c>
@@ -6360,13 +7532,19 @@
         <v>73</v>
       </c>
       <c r="H195">
+        <v>0</v>
+      </c>
+      <c r="I195">
+        <v>5</v>
+      </c>
+      <c r="J195">
         <v>4.4000000000000004</v>
       </c>
-      <c r="I195" t="s">
+      <c r="K195" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>20</v>
       </c>
@@ -6389,13 +7567,19 @@
         <v>44</v>
       </c>
       <c r="H196">
+        <v>4</v>
+      </c>
+      <c r="I196">
+        <v>1</v>
+      </c>
+      <c r="J196">
         <v>1.4</v>
       </c>
-      <c r="I196" t="s">
+      <c r="K196" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>20</v>
       </c>
@@ -6418,13 +7602,19 @@
         <v>22</v>
       </c>
       <c r="H197">
+        <v>1</v>
+      </c>
+      <c r="I197">
+        <v>1</v>
+      </c>
+      <c r="J197">
         <v>0.9</v>
       </c>
-      <c r="I197" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K197" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>20</v>
       </c>
@@ -6447,13 +7637,19 @@
         <v>53</v>
       </c>
       <c r="H198">
+        <v>2</v>
+      </c>
+      <c r="I198">
+        <v>2</v>
+      </c>
+      <c r="J198">
         <v>1.5</v>
       </c>
-      <c r="I198" t="s">
+      <c r="K198" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>20</v>
       </c>
@@ -6476,13 +7672,19 @@
         <v>53</v>
       </c>
       <c r="H199">
-        <v>1</v>
-      </c>
-      <c r="I199" t="s">
+        <v>2</v>
+      </c>
+      <c r="I199">
+        <v>2</v>
+      </c>
+      <c r="J199">
+        <v>1</v>
+      </c>
+      <c r="K199" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>20</v>
       </c>
@@ -6505,13 +7707,19 @@
         <v>19</v>
       </c>
       <c r="H200">
+        <v>0</v>
+      </c>
+      <c r="I200">
+        <v>3</v>
+      </c>
+      <c r="J200">
         <v>2.1</v>
       </c>
-      <c r="I200" t="s">
+      <c r="K200" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>21</v>
       </c>
@@ -6534,13 +7742,19 @@
         <v>55</v>
       </c>
       <c r="H201">
+        <v>3</v>
+      </c>
+      <c r="I201">
+        <v>2</v>
+      </c>
+      <c r="J201">
         <v>1.7</v>
       </c>
-      <c r="I201" t="s">
+      <c r="K201" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>21</v>
       </c>
@@ -6563,13 +7777,19 @@
         <v>53</v>
       </c>
       <c r="H202">
+        <v>2</v>
+      </c>
+      <c r="I202">
+        <v>2</v>
+      </c>
+      <c r="J202">
         <v>1.2</v>
       </c>
-      <c r="I202" t="s">
+      <c r="K202" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>21</v>
       </c>
@@ -6592,13 +7812,19 @@
         <v>53</v>
       </c>
       <c r="H203">
+        <v>2</v>
+      </c>
+      <c r="I203">
+        <v>2</v>
+      </c>
+      <c r="J203">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I203" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K203" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>21</v>
       </c>
@@ -6621,13 +7847,19 @@
         <v>22</v>
       </c>
       <c r="H204">
-        <v>2</v>
-      </c>
-      <c r="I204" t="s">
+        <v>1</v>
+      </c>
+      <c r="I204">
+        <v>1</v>
+      </c>
+      <c r="J204">
+        <v>2</v>
+      </c>
+      <c r="K204" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>21</v>
       </c>
@@ -6650,13 +7882,19 @@
         <v>13</v>
       </c>
       <c r="H205">
+        <v>0</v>
+      </c>
+      <c r="I205">
+        <v>2</v>
+      </c>
+      <c r="J205">
         <v>1.8</v>
       </c>
-      <c r="I205" t="s">
+      <c r="K205" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>21</v>
       </c>
@@ -6679,13 +7917,19 @@
         <v>45</v>
       </c>
       <c r="H206">
+        <v>0</v>
+      </c>
+      <c r="I206">
+        <v>1</v>
+      </c>
+      <c r="J206">
         <v>1.2</v>
       </c>
-      <c r="I206" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K206" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>21</v>
       </c>
@@ -6708,13 +7952,19 @@
         <v>56</v>
       </c>
       <c r="H207">
+        <v>3</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="J207">
         <v>1.6</v>
       </c>
-      <c r="I207" t="s">
+      <c r="K207" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>21</v>
       </c>
@@ -6737,13 +7987,19 @@
         <v>32</v>
       </c>
       <c r="H208">
+        <v>2</v>
+      </c>
+      <c r="I208">
+        <v>1</v>
+      </c>
+      <c r="J208">
         <v>0.8</v>
       </c>
-      <c r="I208" t="s">
+      <c r="K208" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>21</v>
       </c>
@@ -6766,13 +8022,19 @@
         <v>13</v>
       </c>
       <c r="H209">
-        <v>1</v>
-      </c>
-      <c r="I209" t="s">
+        <v>0</v>
+      </c>
+      <c r="I209">
+        <v>2</v>
+      </c>
+      <c r="J209">
+        <v>1</v>
+      </c>
+      <c r="K209" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>21</v>
       </c>
@@ -6795,13 +8057,19 @@
         <v>48</v>
       </c>
       <c r="H210">
+        <v>3</v>
+      </c>
+      <c r="I210">
+        <v>1</v>
+      </c>
+      <c r="J210">
         <v>1.4</v>
       </c>
-      <c r="I210" t="s">
+      <c r="K210" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>22</v>
       </c>
@@ -6824,13 +8092,19 @@
         <v>60</v>
       </c>
       <c r="H211">
-        <v>2</v>
-      </c>
-      <c r="I211" t="s">
+        <v>1</v>
+      </c>
+      <c r="I211">
+        <v>4</v>
+      </c>
+      <c r="J211">
+        <v>2</v>
+      </c>
+      <c r="K211" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>22</v>
       </c>
@@ -6853,13 +8127,19 @@
         <v>13</v>
       </c>
       <c r="H212">
-        <v>2</v>
-      </c>
-      <c r="I212" t="s">
+        <v>0</v>
+      </c>
+      <c r="I212">
+        <v>2</v>
+      </c>
+      <c r="J212">
+        <v>2</v>
+      </c>
+      <c r="K212" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>22</v>
       </c>
@@ -6882,13 +8162,19 @@
         <v>13</v>
       </c>
       <c r="H213">
+        <v>0</v>
+      </c>
+      <c r="I213">
+        <v>2</v>
+      </c>
+      <c r="J213">
         <v>1.3</v>
       </c>
-      <c r="I213" t="s">
+      <c r="K213" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>22</v>
       </c>
@@ -6911,13 +8197,19 @@
         <v>13</v>
       </c>
       <c r="H214">
+        <v>0</v>
+      </c>
+      <c r="I214">
+        <v>2</v>
+      </c>
+      <c r="J214">
         <v>3.4</v>
       </c>
-      <c r="I214" t="s">
+      <c r="K214" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>22</v>
       </c>
@@ -6940,13 +8232,19 @@
         <v>53</v>
       </c>
       <c r="H215">
-        <v>1</v>
-      </c>
-      <c r="I215" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="I215">
+        <v>2</v>
+      </c>
+      <c r="J215">
+        <v>1</v>
+      </c>
+      <c r="K215" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>22</v>
       </c>
@@ -6969,13 +8267,19 @@
         <v>55</v>
       </c>
       <c r="H216">
+        <v>3</v>
+      </c>
+      <c r="I216">
+        <v>2</v>
+      </c>
+      <c r="J216">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I216" t="s">
+      <c r="K216" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>22</v>
       </c>
@@ -6998,13 +8302,19 @@
         <v>50</v>
       </c>
       <c r="H217">
+        <v>1</v>
+      </c>
+      <c r="I217">
+        <v>3</v>
+      </c>
+      <c r="J217">
         <v>1.9</v>
       </c>
-      <c r="I217" t="s">
+      <c r="K217" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>22</v>
       </c>
@@ -7027,13 +8337,19 @@
         <v>55</v>
       </c>
       <c r="H218">
+        <v>3</v>
+      </c>
+      <c r="I218">
+        <v>2</v>
+      </c>
+      <c r="J218">
         <v>0.9</v>
       </c>
-      <c r="I218" t="s">
+      <c r="K218" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>22</v>
       </c>
@@ -7056,13 +8372,19 @@
         <v>78</v>
       </c>
       <c r="H219">
+        <v>0</v>
+      </c>
+      <c r="I219">
+        <v>6</v>
+      </c>
+      <c r="J219">
         <v>3</v>
       </c>
-      <c r="I219" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K219" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>22</v>
       </c>
@@ -7085,13 +8407,19 @@
         <v>48</v>
       </c>
       <c r="H220">
+        <v>3</v>
+      </c>
+      <c r="I220">
+        <v>1</v>
+      </c>
+      <c r="J220">
         <v>0.8</v>
       </c>
-      <c r="I220" t="s">
+      <c r="K220" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>23</v>
       </c>
@@ -7114,13 +8442,19 @@
         <v>50</v>
       </c>
       <c r="H221">
+        <v>1</v>
+      </c>
+      <c r="I221">
+        <v>3</v>
+      </c>
+      <c r="J221">
         <v>2.9</v>
       </c>
-      <c r="I221" t="s">
+      <c r="K221" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>23</v>
       </c>
@@ -7143,13 +8477,19 @@
         <v>45</v>
       </c>
       <c r="H222">
+        <v>0</v>
+      </c>
+      <c r="I222">
+        <v>1</v>
+      </c>
+      <c r="J222">
         <v>0.8</v>
       </c>
-      <c r="I222" t="s">
+      <c r="K222" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>23</v>
       </c>
@@ -7172,13 +8512,19 @@
         <v>44</v>
       </c>
       <c r="H223">
+        <v>4</v>
+      </c>
+      <c r="I223">
+        <v>1</v>
+      </c>
+      <c r="J223">
         <v>0.5</v>
       </c>
-      <c r="I223" t="s">
+      <c r="K223" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>23</v>
       </c>
@@ -7201,13 +8547,19 @@
         <v>79</v>
       </c>
       <c r="H224">
-        <v>1</v>
-      </c>
-      <c r="I224" t="s">
+        <v>5</v>
+      </c>
+      <c r="I224">
+        <v>0</v>
+      </c>
+      <c r="J224">
+        <v>1</v>
+      </c>
+      <c r="K224" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>23</v>
       </c>
@@ -7230,13 +8582,19 @@
         <v>45</v>
       </c>
       <c r="H225">
-        <v>1</v>
-      </c>
-      <c r="I225" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="I225">
+        <v>1</v>
+      </c>
+      <c r="J225">
+        <v>1</v>
+      </c>
+      <c r="K225" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>23</v>
       </c>
@@ -7259,13 +8617,19 @@
         <v>48</v>
       </c>
       <c r="H226">
+        <v>3</v>
+      </c>
+      <c r="I226">
+        <v>1</v>
+      </c>
+      <c r="J226">
         <v>1.8</v>
       </c>
-      <c r="I226" t="s">
+      <c r="K226" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>23</v>
       </c>
@@ -7288,13 +8652,19 @@
         <v>28</v>
       </c>
       <c r="H227">
+        <v>1</v>
+      </c>
+      <c r="I227">
+        <v>2</v>
+      </c>
+      <c r="J227">
         <v>1.3</v>
       </c>
-      <c r="I227" t="s">
+      <c r="K227" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>23</v>
       </c>
@@ -7317,13 +8687,19 @@
         <v>28</v>
       </c>
       <c r="H228">
+        <v>1</v>
+      </c>
+      <c r="I228">
+        <v>2</v>
+      </c>
+      <c r="J228">
         <v>1.6</v>
       </c>
-      <c r="I228" t="s">
+      <c r="K228" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>23</v>
       </c>
@@ -7346,13 +8722,19 @@
         <v>22</v>
       </c>
       <c r="H229">
+        <v>1</v>
+      </c>
+      <c r="I229">
+        <v>1</v>
+      </c>
+      <c r="J229">
         <v>1.3</v>
       </c>
-      <c r="I229" t="s">
+      <c r="K229" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>23</v>
       </c>
@@ -7375,13 +8757,19 @@
         <v>45</v>
       </c>
       <c r="H230">
+        <v>0</v>
+      </c>
+      <c r="I230">
+        <v>1</v>
+      </c>
+      <c r="J230">
         <v>0.3</v>
       </c>
-      <c r="I230" t="s">
+      <c r="K230" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>24</v>
       </c>
@@ -7404,13 +8792,19 @@
         <v>80</v>
       </c>
       <c r="H231">
+        <v>7</v>
+      </c>
+      <c r="I231">
+        <v>0</v>
+      </c>
+      <c r="J231">
         <v>0.9</v>
       </c>
-      <c r="I231" t="s">
+      <c r="K231" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>24</v>
       </c>
@@ -7433,13 +8827,19 @@
         <v>46</v>
       </c>
       <c r="H232">
+        <v>4</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
         <v>0.3</v>
       </c>
-      <c r="I232" t="s">
+      <c r="K232" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>24</v>
       </c>
@@ -7462,13 +8862,19 @@
         <v>28</v>
       </c>
       <c r="H233">
+        <v>1</v>
+      </c>
+      <c r="I233">
+        <v>2</v>
+      </c>
+      <c r="J233">
         <v>1.6</v>
       </c>
-      <c r="I233" t="s">
+      <c r="K233" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>24</v>
       </c>
@@ -7491,13 +8897,19 @@
         <v>13</v>
       </c>
       <c r="H234">
+        <v>0</v>
+      </c>
+      <c r="I234">
+        <v>2</v>
+      </c>
+      <c r="J234">
         <v>2.5</v>
       </c>
-      <c r="I234" t="s">
+      <c r="K234" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>24</v>
       </c>
@@ -7520,13 +8932,19 @@
         <v>28</v>
       </c>
       <c r="H235">
+        <v>1</v>
+      </c>
+      <c r="I235">
+        <v>2</v>
+      </c>
+      <c r="J235">
         <v>0.9</v>
       </c>
-      <c r="I235" t="s">
+      <c r="K235" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>24</v>
       </c>
@@ -7549,13 +8967,19 @@
         <v>24</v>
       </c>
       <c r="H236">
+        <v>2</v>
+      </c>
+      <c r="I236">
+        <v>0</v>
+      </c>
+      <c r="J236">
         <v>0.4</v>
       </c>
-      <c r="I236" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K236" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>24</v>
       </c>
@@ -7578,13 +9002,19 @@
         <v>13</v>
       </c>
       <c r="H237">
+        <v>0</v>
+      </c>
+      <c r="I237">
+        <v>2</v>
+      </c>
+      <c r="J237">
         <v>2.6</v>
       </c>
-      <c r="I237" t="s">
+      <c r="K237" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>24</v>
       </c>
@@ -7607,13 +9037,19 @@
         <v>13</v>
       </c>
       <c r="H238">
+        <v>0</v>
+      </c>
+      <c r="I238">
+        <v>2</v>
+      </c>
+      <c r="J238">
         <v>0.8</v>
       </c>
-      <c r="I238" t="s">
+      <c r="K238" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>24</v>
       </c>
@@ -7636,13 +9072,19 @@
         <v>81</v>
       </c>
       <c r="H239">
+        <v>5</v>
+      </c>
+      <c r="I239">
+        <v>1</v>
+      </c>
+      <c r="J239">
         <v>0.8</v>
       </c>
-      <c r="I239" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K239" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>24</v>
       </c>
@@ -7665,13 +9107,19 @@
         <v>32</v>
       </c>
       <c r="H240">
+        <v>2</v>
+      </c>
+      <c r="I240">
+        <v>1</v>
+      </c>
+      <c r="J240">
         <v>1.2</v>
       </c>
-      <c r="I240" t="s">
+      <c r="K240" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>15</v>
       </c>
@@ -7694,13 +9142,19 @@
         <v>53</v>
       </c>
       <c r="H241">
+        <v>2</v>
+      </c>
+      <c r="I241">
+        <v>2</v>
+      </c>
+      <c r="J241">
         <v>0.6</v>
       </c>
-      <c r="I241" t="s">
+      <c r="K241" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>25</v>
       </c>
@@ -7723,13 +9177,19 @@
         <v>56</v>
       </c>
       <c r="H242">
+        <v>3</v>
+      </c>
+      <c r="I242">
+        <v>0</v>
+      </c>
+      <c r="J242">
         <v>0.5</v>
       </c>
-      <c r="I242" t="s">
+      <c r="K242" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>25</v>
       </c>
@@ -7752,13 +9212,19 @@
         <v>13</v>
       </c>
       <c r="H243">
+        <v>0</v>
+      </c>
+      <c r="I243">
+        <v>2</v>
+      </c>
+      <c r="J243">
         <v>1.4</v>
       </c>
-      <c r="I243" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K243" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>25</v>
       </c>
@@ -7781,13 +9247,19 @@
         <v>32</v>
       </c>
       <c r="H244">
+        <v>2</v>
+      </c>
+      <c r="I244">
+        <v>1</v>
+      </c>
+      <c r="J244">
         <v>0.4</v>
       </c>
-      <c r="I244" t="s">
+      <c r="K244" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>25</v>
       </c>
@@ -7810,13 +9282,19 @@
         <v>46</v>
       </c>
       <c r="H245">
+        <v>4</v>
+      </c>
+      <c r="I245">
+        <v>0</v>
+      </c>
+      <c r="J245">
         <v>0.5</v>
       </c>
-      <c r="I245" t="s">
+      <c r="K245" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>25</v>
       </c>
@@ -7839,13 +9317,19 @@
         <v>50</v>
       </c>
       <c r="H246">
+        <v>1</v>
+      </c>
+      <c r="I246">
+        <v>3</v>
+      </c>
+      <c r="J246">
         <v>1.2</v>
       </c>
-      <c r="I246" t="s">
+      <c r="K246" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>25</v>
       </c>
@@ -7868,13 +9352,19 @@
         <v>22</v>
       </c>
       <c r="H247">
+        <v>1</v>
+      </c>
+      <c r="I247">
+        <v>1</v>
+      </c>
+      <c r="J247">
         <v>0.4</v>
       </c>
-      <c r="I247" t="s">
+      <c r="K247" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>25</v>
       </c>
@@ -7897,13 +9387,19 @@
         <v>45</v>
       </c>
       <c r="H248">
+        <v>0</v>
+      </c>
+      <c r="I248">
+        <v>1</v>
+      </c>
+      <c r="J248">
         <v>1.6</v>
       </c>
-      <c r="I248" t="s">
+      <c r="K248" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>25</v>
       </c>
@@ -7926,13 +9422,19 @@
         <v>28</v>
       </c>
       <c r="H249">
+        <v>1</v>
+      </c>
+      <c r="I249">
+        <v>2</v>
+      </c>
+      <c r="J249">
         <v>0.9</v>
       </c>
-      <c r="I249" t="s">
+      <c r="K249" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>25</v>
       </c>
@@ -7955,13 +9457,19 @@
         <v>32</v>
       </c>
       <c r="H250">
+        <v>2</v>
+      </c>
+      <c r="I250">
+        <v>1</v>
+      </c>
+      <c r="J250">
         <v>1.5</v>
       </c>
-      <c r="I250" t="s">
+      <c r="K250" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>25</v>
       </c>
@@ -7984,13 +9492,19 @@
         <v>8</v>
       </c>
       <c r="H251">
+        <v>1</v>
+      </c>
+      <c r="I251">
+        <v>0</v>
+      </c>
+      <c r="J251">
         <v>1.5</v>
       </c>
-      <c r="I251" t="s">
+      <c r="K251" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>29</v>
       </c>
@@ -8013,13 +9527,19 @@
         <v>53</v>
       </c>
       <c r="H252">
+        <v>2</v>
+      </c>
+      <c r="I252">
+        <v>2</v>
+      </c>
+      <c r="J252">
         <v>2.5</v>
       </c>
-      <c r="I252" t="s">
+      <c r="K252" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>26</v>
       </c>
@@ -8042,13 +9562,19 @@
         <v>61</v>
       </c>
       <c r="H253">
+        <v>0</v>
+      </c>
+      <c r="I253">
+        <v>4</v>
+      </c>
+      <c r="J253">
         <v>1.5</v>
       </c>
-      <c r="I253" t="s">
+      <c r="K253" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>26</v>
       </c>
@@ -8071,13 +9597,19 @@
         <v>53</v>
       </c>
       <c r="H254">
+        <v>2</v>
+      </c>
+      <c r="I254">
+        <v>2</v>
+      </c>
+      <c r="J254">
         <v>0.4</v>
       </c>
-      <c r="I254" t="s">
+      <c r="K254" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>26</v>
       </c>
@@ -8100,13 +9632,19 @@
         <v>13</v>
       </c>
       <c r="H255">
+        <v>0</v>
+      </c>
+      <c r="I255">
+        <v>2</v>
+      </c>
+      <c r="J255">
         <v>1.3</v>
       </c>
-      <c r="I255" t="s">
+      <c r="K255" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>26</v>
       </c>
@@ -8129,13 +9667,19 @@
         <v>45</v>
       </c>
       <c r="H256">
-        <v>2</v>
-      </c>
-      <c r="I256" t="s">
+        <v>0</v>
+      </c>
+      <c r="I256">
+        <v>1</v>
+      </c>
+      <c r="J256">
+        <v>2</v>
+      </c>
+      <c r="K256" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>26</v>
       </c>
@@ -8158,13 +9702,19 @@
         <v>60</v>
       </c>
       <c r="H257">
+        <v>1</v>
+      </c>
+      <c r="I257">
+        <v>4</v>
+      </c>
+      <c r="J257">
         <v>1.7</v>
       </c>
-      <c r="I257" t="s">
+      <c r="K257" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>26</v>
       </c>
@@ -8187,13 +9737,19 @@
         <v>45</v>
       </c>
       <c r="H258">
+        <v>0</v>
+      </c>
+      <c r="I258">
+        <v>1</v>
+      </c>
+      <c r="J258">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I258" t="s">
+      <c r="K258" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>26</v>
       </c>
@@ -8216,13 +9772,19 @@
         <v>61</v>
       </c>
       <c r="H259">
+        <v>0</v>
+      </c>
+      <c r="I259">
+        <v>4</v>
+      </c>
+      <c r="J259">
         <v>3.9</v>
       </c>
-      <c r="I259" t="s">
+      <c r="K259" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>26</v>
       </c>
@@ -8245,13 +9807,19 @@
         <v>32</v>
       </c>
       <c r="H260">
+        <v>2</v>
+      </c>
+      <c r="I260">
+        <v>1</v>
+      </c>
+      <c r="J260">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I260" t="s">
+      <c r="K260" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>26</v>
       </c>
@@ -8274,13 +9842,19 @@
         <v>59</v>
       </c>
       <c r="H261">
+        <v>4</v>
+      </c>
+      <c r="I261">
+        <v>3</v>
+      </c>
+      <c r="J261">
         <v>1.7</v>
       </c>
-      <c r="I261" t="s">
+      <c r="K261" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>26</v>
       </c>
@@ -8303,13 +9877,19 @@
         <v>13</v>
       </c>
       <c r="H262">
+        <v>0</v>
+      </c>
+      <c r="I262">
+        <v>2</v>
+      </c>
+      <c r="J262">
         <v>0.7</v>
       </c>
-      <c r="I262" t="s">
+      <c r="K262" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>27</v>
       </c>
@@ -8332,13 +9912,19 @@
         <v>32</v>
       </c>
       <c r="H263">
+        <v>2</v>
+      </c>
+      <c r="I263">
+        <v>1</v>
+      </c>
+      <c r="J263">
         <v>1.5</v>
       </c>
-      <c r="I263" t="s">
+      <c r="K263" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>27</v>
       </c>
@@ -8361,13 +9947,19 @@
         <v>44</v>
       </c>
       <c r="H264">
+        <v>4</v>
+      </c>
+      <c r="I264">
+        <v>1</v>
+      </c>
+      <c r="J264">
         <v>0.4</v>
       </c>
-      <c r="I264" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K264" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>27</v>
       </c>
@@ -8390,13 +9982,19 @@
         <v>28</v>
       </c>
       <c r="H265">
+        <v>1</v>
+      </c>
+      <c r="I265">
+        <v>2</v>
+      </c>
+      <c r="J265">
         <v>1.7</v>
       </c>
-      <c r="I265" t="s">
+      <c r="K265" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>27</v>
       </c>
@@ -8419,13 +10017,19 @@
         <v>46</v>
       </c>
       <c r="H266">
+        <v>4</v>
+      </c>
+      <c r="I266">
+        <v>0</v>
+      </c>
+      <c r="J266">
         <v>0.7</v>
       </c>
-      <c r="I266" t="s">
+      <c r="K266" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>27</v>
       </c>
@@ -8448,13 +10052,19 @@
         <v>45</v>
       </c>
       <c r="H267">
+        <v>0</v>
+      </c>
+      <c r="I267">
+        <v>1</v>
+      </c>
+      <c r="J267">
         <v>2.1</v>
       </c>
-      <c r="I267" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K267" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>27</v>
       </c>
@@ -8477,13 +10087,19 @@
         <v>54</v>
       </c>
       <c r="H268">
-        <v>1</v>
-      </c>
-      <c r="I268" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="I268">
+        <v>0</v>
+      </c>
+      <c r="J268">
+        <v>1</v>
+      </c>
+      <c r="K268" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>27</v>
       </c>
@@ -8506,13 +10122,19 @@
         <v>55</v>
       </c>
       <c r="H269">
+        <v>3</v>
+      </c>
+      <c r="I269">
+        <v>2</v>
+      </c>
+      <c r="J269">
         <v>1.4</v>
       </c>
-      <c r="I269" t="s">
+      <c r="K269" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>27</v>
       </c>
@@ -8535,13 +10157,19 @@
         <v>22</v>
       </c>
       <c r="H270">
+        <v>1</v>
+      </c>
+      <c r="I270">
+        <v>1</v>
+      </c>
+      <c r="J270">
         <v>1.5</v>
       </c>
-      <c r="I270" t="s">
+      <c r="K270" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>27</v>
       </c>
@@ -8564,13 +10192,19 @@
         <v>24</v>
       </c>
       <c r="H271">
+        <v>2</v>
+      </c>
+      <c r="I271">
+        <v>0</v>
+      </c>
+      <c r="J271">
         <v>0.2</v>
       </c>
-      <c r="I271" t="s">
+      <c r="K271" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>27</v>
       </c>
@@ -8593,13 +10227,19 @@
         <v>24</v>
       </c>
       <c r="H272">
+        <v>2</v>
+      </c>
+      <c r="I272">
+        <v>0</v>
+      </c>
+      <c r="J272">
         <v>0.4</v>
       </c>
-      <c r="I272" t="s">
+      <c r="K272" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>28</v>
       </c>
@@ -8622,13 +10262,19 @@
         <v>8</v>
       </c>
       <c r="H273">
+        <v>1</v>
+      </c>
+      <c r="I273">
+        <v>0</v>
+      </c>
+      <c r="J273">
         <v>0.9</v>
       </c>
-      <c r="I273" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K273" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>28</v>
       </c>
@@ -8651,13 +10297,19 @@
         <v>48</v>
       </c>
       <c r="H274">
+        <v>3</v>
+      </c>
+      <c r="I274">
+        <v>1</v>
+      </c>
+      <c r="J274">
         <v>0.4</v>
       </c>
-      <c r="I274" t="s">
+      <c r="K274" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>28</v>
       </c>
@@ -8680,13 +10332,19 @@
         <v>32</v>
       </c>
       <c r="H275">
+        <v>2</v>
+      </c>
+      <c r="I275">
+        <v>1</v>
+      </c>
+      <c r="J275">
         <v>0.9</v>
       </c>
-      <c r="I275" t="s">
+      <c r="K275" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>28</v>
       </c>
@@ -8709,13 +10367,19 @@
         <v>8</v>
       </c>
       <c r="H276">
+        <v>1</v>
+      </c>
+      <c r="I276">
+        <v>0</v>
+      </c>
+      <c r="J276">
         <v>1.5</v>
       </c>
-      <c r="I276" t="s">
+      <c r="K276" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>28</v>
       </c>
@@ -8738,13 +10402,19 @@
         <v>45</v>
       </c>
       <c r="H277">
+        <v>0</v>
+      </c>
+      <c r="I277">
+        <v>1</v>
+      </c>
+      <c r="J277">
         <v>1.3</v>
       </c>
-      <c r="I277" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K277" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>28</v>
       </c>
@@ -8767,13 +10437,19 @@
         <v>22</v>
       </c>
       <c r="H278">
+        <v>1</v>
+      </c>
+      <c r="I278">
+        <v>1</v>
+      </c>
+      <c r="J278">
         <v>1.2</v>
       </c>
-      <c r="I278" t="s">
+      <c r="K278" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>28</v>
       </c>
@@ -8796,13 +10472,19 @@
         <v>8</v>
       </c>
       <c r="H279">
+        <v>1</v>
+      </c>
+      <c r="I279">
+        <v>0</v>
+      </c>
+      <c r="J279">
         <v>0.1</v>
       </c>
-      <c r="I279" t="s">
+      <c r="K279" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>28</v>
       </c>
@@ -8825,13 +10507,19 @@
         <v>53</v>
       </c>
       <c r="H280">
+        <v>2</v>
+      </c>
+      <c r="I280">
+        <v>2</v>
+      </c>
+      <c r="J280">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I280" t="s">
+      <c r="K280" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>28</v>
       </c>
@@ -8854,13 +10542,19 @@
         <v>22</v>
       </c>
       <c r="H281">
+        <v>1</v>
+      </c>
+      <c r="I281">
+        <v>1</v>
+      </c>
+      <c r="J281">
         <v>1.6</v>
       </c>
-      <c r="I281" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K281" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>28</v>
       </c>
@@ -8883,13 +10577,19 @@
         <v>45</v>
       </c>
       <c r="H282">
+        <v>0</v>
+      </c>
+      <c r="I282">
+        <v>1</v>
+      </c>
+      <c r="J282">
         <v>1.4</v>
       </c>
-      <c r="I282" t="s">
+      <c r="K282" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>29</v>
       </c>
@@ -8912,13 +10612,19 @@
         <v>22</v>
       </c>
       <c r="H283">
+        <v>1</v>
+      </c>
+      <c r="I283">
+        <v>1</v>
+      </c>
+      <c r="J283">
         <v>0.8</v>
       </c>
-      <c r="I283" t="s">
+      <c r="K283" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>29</v>
       </c>
@@ -8941,13 +10647,19 @@
         <v>28</v>
       </c>
       <c r="H284">
+        <v>1</v>
+      </c>
+      <c r="I284">
+        <v>2</v>
+      </c>
+      <c r="J284">
         <v>0.4</v>
       </c>
-      <c r="I284" t="s">
+      <c r="K284" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>29</v>
       </c>
@@ -8970,13 +10682,19 @@
         <v>62</v>
       </c>
       <c r="H285">
+        <v>2</v>
+      </c>
+      <c r="I285">
+        <v>4</v>
+      </c>
+      <c r="J285">
         <v>1.5</v>
       </c>
-      <c r="I285" t="s">
+      <c r="K285" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>29</v>
       </c>
@@ -9001,11 +10719,17 @@
       <c r="H286">
         <v>2</v>
       </c>
-      <c r="I286" t="s">
+      <c r="I286">
+        <v>2</v>
+      </c>
+      <c r="J286">
+        <v>2</v>
+      </c>
+      <c r="K286" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>29</v>
       </c>
@@ -9028,13 +10752,19 @@
         <v>28</v>
       </c>
       <c r="H287">
+        <v>1</v>
+      </c>
+      <c r="I287">
+        <v>2</v>
+      </c>
+      <c r="J287">
         <v>0.8</v>
       </c>
-      <c r="I287" t="s">
+      <c r="K287" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>29</v>
       </c>
@@ -9057,13 +10787,19 @@
         <v>8</v>
       </c>
       <c r="H288">
+        <v>1</v>
+      </c>
+      <c r="I288">
+        <v>0</v>
+      </c>
+      <c r="J288">
         <v>0.4</v>
       </c>
-      <c r="I288" t="s">
+      <c r="K288" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>29</v>
       </c>
@@ -9086,13 +10822,19 @@
         <v>24</v>
       </c>
       <c r="H289">
+        <v>2</v>
+      </c>
+      <c r="I289">
+        <v>0</v>
+      </c>
+      <c r="J289">
         <v>0.9</v>
       </c>
-      <c r="I289" t="s">
+      <c r="K289" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>29</v>
       </c>
@@ -9115,13 +10857,19 @@
         <v>19</v>
       </c>
       <c r="H290">
+        <v>0</v>
+      </c>
+      <c r="I290">
+        <v>3</v>
+      </c>
+      <c r="J290">
         <v>0.9</v>
       </c>
-      <c r="I290" t="s">
+      <c r="K290" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>30</v>
       </c>
@@ -9144,13 +10892,19 @@
         <v>32</v>
       </c>
       <c r="H291">
-        <v>1</v>
-      </c>
-      <c r="I291" t="s">
+        <v>2</v>
+      </c>
+      <c r="I291">
+        <v>1</v>
+      </c>
+      <c r="J291">
+        <v>1</v>
+      </c>
+      <c r="K291" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>30</v>
       </c>
@@ -9173,13 +10927,19 @@
         <v>8</v>
       </c>
       <c r="H292">
+        <v>1</v>
+      </c>
+      <c r="I292">
+        <v>0</v>
+      </c>
+      <c r="J292">
         <v>1.3</v>
       </c>
-      <c r="I292" t="s">
+      <c r="K292" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>30</v>
       </c>
@@ -9202,13 +10962,19 @@
         <v>8</v>
       </c>
       <c r="H293">
+        <v>1</v>
+      </c>
+      <c r="I293">
+        <v>0</v>
+      </c>
+      <c r="J293">
         <v>1.6</v>
       </c>
-      <c r="I293" t="s">
+      <c r="K293" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>30</v>
       </c>
@@ -9231,13 +10997,19 @@
         <v>32</v>
       </c>
       <c r="H294">
+        <v>2</v>
+      </c>
+      <c r="I294">
+        <v>1</v>
+      </c>
+      <c r="J294">
         <v>1.5</v>
       </c>
-      <c r="I294" t="s">
+      <c r="K294" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>30</v>
       </c>
@@ -9260,13 +11032,19 @@
         <v>24</v>
       </c>
       <c r="H295">
+        <v>2</v>
+      </c>
+      <c r="I295">
+        <v>0</v>
+      </c>
+      <c r="J295">
         <v>0.1</v>
       </c>
-      <c r="I295" t="s">
+      <c r="K295" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>30</v>
       </c>
@@ -9289,13 +11067,19 @@
         <v>22</v>
       </c>
       <c r="H296">
+        <v>1</v>
+      </c>
+      <c r="I296">
+        <v>1</v>
+      </c>
+      <c r="J296">
         <v>0.7</v>
       </c>
-      <c r="I296" t="s">
+      <c r="K296" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>30</v>
       </c>
@@ -9318,13 +11102,19 @@
         <v>28</v>
       </c>
       <c r="H297">
+        <v>1</v>
+      </c>
+      <c r="I297">
+        <v>2</v>
+      </c>
+      <c r="J297">
         <v>1.2</v>
       </c>
-      <c r="I297" t="s">
+      <c r="K297" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>30</v>
       </c>
@@ -9347,13 +11137,19 @@
         <v>19</v>
       </c>
       <c r="H298">
+        <v>0</v>
+      </c>
+      <c r="I298">
+        <v>3</v>
+      </c>
+      <c r="J298">
         <v>1.2</v>
       </c>
-      <c r="I298" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K298" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>30</v>
       </c>
@@ -9376,13 +11172,19 @@
         <v>8</v>
       </c>
       <c r="H299">
+        <v>1</v>
+      </c>
+      <c r="I299">
+        <v>0</v>
+      </c>
+      <c r="J299">
         <v>0.9</v>
       </c>
-      <c r="I299" t="s">
+      <c r="K299" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>30</v>
       </c>
@@ -9405,13 +11207,19 @@
         <v>8</v>
       </c>
       <c r="H300">
+        <v>1</v>
+      </c>
+      <c r="I300">
+        <v>0</v>
+      </c>
+      <c r="J300">
         <v>0.9</v>
       </c>
-      <c r="I300" t="s">
+      <c r="K300" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>31</v>
       </c>
@@ -9434,13 +11242,19 @@
         <v>22</v>
       </c>
       <c r="H301">
+        <v>1</v>
+      </c>
+      <c r="I301">
+        <v>1</v>
+      </c>
+      <c r="J301">
         <v>1.8</v>
       </c>
-      <c r="I301" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K301" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>31</v>
       </c>
@@ -9463,13 +11277,19 @@
         <v>32</v>
       </c>
       <c r="H302">
-        <v>1</v>
-      </c>
-      <c r="I302" t="s">
+        <v>2</v>
+      </c>
+      <c r="I302">
+        <v>1</v>
+      </c>
+      <c r="J302">
+        <v>1</v>
+      </c>
+      <c r="K302" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>31</v>
       </c>
@@ -9492,13 +11312,19 @@
         <v>28</v>
       </c>
       <c r="H303">
+        <v>1</v>
+      </c>
+      <c r="I303">
+        <v>2</v>
+      </c>
+      <c r="J303">
         <v>2.6</v>
       </c>
-      <c r="I303" t="s">
+      <c r="K303" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>31</v>
       </c>
@@ -9521,13 +11347,19 @@
         <v>53</v>
       </c>
       <c r="H304">
+        <v>2</v>
+      </c>
+      <c r="I304">
+        <v>2</v>
+      </c>
+      <c r="J304">
         <v>2.1</v>
       </c>
-      <c r="I304" t="s">
+      <c r="K304" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>31</v>
       </c>
@@ -9550,13 +11382,19 @@
         <v>32</v>
       </c>
       <c r="H305">
+        <v>2</v>
+      </c>
+      <c r="I305">
+        <v>1</v>
+      </c>
+      <c r="J305">
         <v>1.5</v>
       </c>
-      <c r="I305" t="s">
+      <c r="K305" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>31</v>
       </c>
@@ -9579,13 +11417,19 @@
         <v>55</v>
       </c>
       <c r="H306">
+        <v>3</v>
+      </c>
+      <c r="I306">
+        <v>2</v>
+      </c>
+      <c r="J306">
         <v>1.5</v>
       </c>
-      <c r="I306" t="s">
+      <c r="K306" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>31</v>
       </c>
@@ -9608,13 +11452,19 @@
         <v>54</v>
       </c>
       <c r="H307">
+        <v>0</v>
+      </c>
+      <c r="I307">
+        <v>0</v>
+      </c>
+      <c r="J307">
         <v>1.2</v>
       </c>
-      <c r="I307" t="s">
+      <c r="K307" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>31</v>
       </c>
@@ -9637,13 +11487,19 @@
         <v>48</v>
       </c>
       <c r="H308">
-        <v>1</v>
-      </c>
-      <c r="I308" t="s">
+        <v>3</v>
+      </c>
+      <c r="I308">
+        <v>1</v>
+      </c>
+      <c r="J308">
+        <v>1</v>
+      </c>
+      <c r="K308" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>31</v>
       </c>
@@ -9666,13 +11522,19 @@
         <v>54</v>
       </c>
       <c r="H309">
+        <v>0</v>
+      </c>
+      <c r="I309">
+        <v>0</v>
+      </c>
+      <c r="J309">
         <v>0.5</v>
       </c>
-      <c r="I309" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K309" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>31</v>
       </c>
@@ -9695,13 +11557,19 @@
         <v>19</v>
       </c>
       <c r="H310">
+        <v>0</v>
+      </c>
+      <c r="I310">
+        <v>3</v>
+      </c>
+      <c r="J310">
         <v>3.2</v>
       </c>
-      <c r="I310" t="s">
+      <c r="K310" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>32</v>
       </c>
@@ -9724,13 +11592,19 @@
         <v>82</v>
       </c>
       <c r="H311">
+        <v>5</v>
+      </c>
+      <c r="I311">
+        <v>2</v>
+      </c>
+      <c r="J311">
         <v>1.8</v>
       </c>
-      <c r="I311" t="s">
+      <c r="K311" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>32</v>
       </c>
@@ -9753,13 +11627,19 @@
         <v>53</v>
       </c>
       <c r="H312">
+        <v>2</v>
+      </c>
+      <c r="I312">
+        <v>2</v>
+      </c>
+      <c r="J312">
         <v>1.5</v>
       </c>
-      <c r="I312" t="s">
+      <c r="K312" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>32</v>
       </c>
@@ -9782,13 +11662,19 @@
         <v>19</v>
       </c>
       <c r="H313">
+        <v>0</v>
+      </c>
+      <c r="I313">
         <v>3</v>
       </c>
-      <c r="I313" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J313">
+        <v>3</v>
+      </c>
+      <c r="K313" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>32</v>
       </c>
@@ -9811,13 +11697,19 @@
         <v>45</v>
       </c>
       <c r="H314">
+        <v>0</v>
+      </c>
+      <c r="I314">
+        <v>1</v>
+      </c>
+      <c r="J314">
         <v>1.4</v>
       </c>
-      <c r="I314" t="s">
+      <c r="K314" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>32</v>
       </c>
@@ -9840,13 +11732,19 @@
         <v>22</v>
       </c>
       <c r="H315">
+        <v>1</v>
+      </c>
+      <c r="I315">
+        <v>1</v>
+      </c>
+      <c r="J315">
         <v>0.2</v>
       </c>
-      <c r="I315" t="s">
+      <c r="K315" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>32</v>
       </c>
@@ -9869,13 +11767,19 @@
         <v>32</v>
       </c>
       <c r="H316">
+        <v>2</v>
+      </c>
+      <c r="I316">
+        <v>1</v>
+      </c>
+      <c r="J316">
         <v>1.4</v>
       </c>
-      <c r="I316" t="s">
+      <c r="K316" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>32</v>
       </c>
@@ -9898,13 +11802,19 @@
         <v>53</v>
       </c>
       <c r="H317">
+        <v>2</v>
+      </c>
+      <c r="I317">
+        <v>2</v>
+      </c>
+      <c r="J317">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I317" t="s">
+      <c r="K317" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>32</v>
       </c>
@@ -9927,13 +11837,19 @@
         <v>57</v>
       </c>
       <c r="H318">
-        <v>2</v>
-      </c>
-      <c r="I318" t="s">
+        <v>4</v>
+      </c>
+      <c r="I318">
+        <v>2</v>
+      </c>
+      <c r="J318">
+        <v>2</v>
+      </c>
+      <c r="K318" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>32</v>
       </c>
@@ -9956,13 +11872,19 @@
         <v>44</v>
       </c>
       <c r="H319">
+        <v>4</v>
+      </c>
+      <c r="I319">
+        <v>1</v>
+      </c>
+      <c r="J319">
         <v>0.7</v>
       </c>
-      <c r="I319" t="s">
+      <c r="K319" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>32</v>
       </c>
@@ -9987,11 +11909,17 @@
       <c r="H320">
         <v>1</v>
       </c>
-      <c r="I320" t="s">
+      <c r="I320">
+        <v>0</v>
+      </c>
+      <c r="J320">
+        <v>1</v>
+      </c>
+      <c r="K320" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>29</v>
       </c>
@@ -10014,13 +11942,19 @@
         <v>79</v>
       </c>
       <c r="H321">
-        <v>2</v>
-      </c>
-      <c r="I321" t="s">
+        <v>5</v>
+      </c>
+      <c r="I321">
+        <v>0</v>
+      </c>
+      <c r="J321">
+        <v>2</v>
+      </c>
+      <c r="K321" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>33</v>
       </c>
@@ -10043,13 +11977,19 @@
         <v>13</v>
       </c>
       <c r="H322">
-        <v>2</v>
-      </c>
-      <c r="I322" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="I322">
+        <v>2</v>
+      </c>
+      <c r="J322">
+        <v>2</v>
+      </c>
+      <c r="K322" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>33</v>
       </c>
@@ -10072,13 +12012,19 @@
         <v>22</v>
       </c>
       <c r="H323">
+        <v>1</v>
+      </c>
+      <c r="I323">
+        <v>1</v>
+      </c>
+      <c r="J323">
         <v>0.6</v>
       </c>
-      <c r="I323" t="s">
+      <c r="K323" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>33</v>
       </c>
@@ -10101,13 +12047,19 @@
         <v>54</v>
       </c>
       <c r="H324">
+        <v>0</v>
+      </c>
+      <c r="I324">
+        <v>0</v>
+      </c>
+      <c r="J324">
         <v>0.7</v>
       </c>
-      <c r="I324" t="s">
+      <c r="K324" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>33</v>
       </c>
@@ -10130,13 +12082,19 @@
         <v>57</v>
       </c>
       <c r="H325">
+        <v>4</v>
+      </c>
+      <c r="I325">
+        <v>2</v>
+      </c>
+      <c r="J325">
         <v>1.4</v>
       </c>
-      <c r="I325" t="s">
+      <c r="K325" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>33</v>
       </c>
@@ -10159,13 +12117,19 @@
         <v>44</v>
       </c>
       <c r="H326">
-        <v>1</v>
-      </c>
-      <c r="I326" t="s">
+        <v>4</v>
+      </c>
+      <c r="I326">
+        <v>1</v>
+      </c>
+      <c r="J326">
+        <v>1</v>
+      </c>
+      <c r="K326" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>33</v>
       </c>
@@ -10188,13 +12152,19 @@
         <v>28</v>
       </c>
       <c r="H327">
+        <v>1</v>
+      </c>
+      <c r="I327">
+        <v>2</v>
+      </c>
+      <c r="J327">
         <v>0.9</v>
       </c>
-      <c r="I327" t="s">
+      <c r="K327" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>33</v>
       </c>
@@ -10217,13 +12187,19 @@
         <v>61</v>
       </c>
       <c r="H328">
+        <v>0</v>
+      </c>
+      <c r="I328">
+        <v>4</v>
+      </c>
+      <c r="J328">
         <v>2.4</v>
       </c>
-      <c r="I328" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K328" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>33</v>
       </c>
@@ -10246,13 +12222,19 @@
         <v>45</v>
       </c>
       <c r="H329">
+        <v>0</v>
+      </c>
+      <c r="I329">
+        <v>1</v>
+      </c>
+      <c r="J329">
         <v>0.2</v>
       </c>
-      <c r="I329" t="s">
+      <c r="K329" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>33</v>
       </c>
@@ -10275,13 +12257,19 @@
         <v>45</v>
       </c>
       <c r="H330">
+        <v>0</v>
+      </c>
+      <c r="I330">
+        <v>1</v>
+      </c>
+      <c r="J330">
         <v>2.5</v>
       </c>
-      <c r="I330" t="s">
+      <c r="K330" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>33</v>
       </c>
@@ -10304,13 +12292,19 @@
         <v>28</v>
       </c>
       <c r="H331">
+        <v>1</v>
+      </c>
+      <c r="I331">
+        <v>2</v>
+      </c>
+      <c r="J331">
         <v>0.5</v>
       </c>
-      <c r="I331" t="s">
+      <c r="K331" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>34</v>
       </c>
@@ -10333,14 +12327,20 @@
         <v>32</v>
       </c>
       <c r="H332">
+        <v>2</v>
+      </c>
+      <c r="I332">
+        <v>1</v>
+      </c>
+      <c r="J332">
         <v>1.8</v>
       </c>
-      <c r="I332" t="s">
-        <v>1</v>
-      </c>
-      <c r="J332" s="2"/>
-    </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K332" t="s">
+        <v>1</v>
+      </c>
+      <c r="L332" s="2"/>
+    </row>
+    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>34</v>
       </c>
@@ -10363,14 +12363,20 @@
         <v>53</v>
       </c>
       <c r="H333">
+        <v>2</v>
+      </c>
+      <c r="I333">
+        <v>2</v>
+      </c>
+      <c r="J333">
         <v>1.7</v>
       </c>
-      <c r="I333" t="s">
+      <c r="K333" t="s">
         <v>33</v>
       </c>
-      <c r="J333" s="2"/>
-    </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L333" s="2"/>
+    </row>
+    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>34</v>
       </c>
@@ -10393,14 +12399,20 @@
         <v>8</v>
       </c>
       <c r="H334">
+        <v>1</v>
+      </c>
+      <c r="I334">
+        <v>0</v>
+      </c>
+      <c r="J334">
         <v>0.4</v>
       </c>
-      <c r="I334" t="s">
+      <c r="K334" t="s">
         <v>18</v>
       </c>
-      <c r="J334" s="2"/>
-    </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L334" s="2"/>
+    </row>
+    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>34</v>
       </c>
@@ -10423,14 +12435,20 @@
         <v>55</v>
       </c>
       <c r="H335">
+        <v>3</v>
+      </c>
+      <c r="I335">
+        <v>2</v>
+      </c>
+      <c r="J335">
         <v>1.3</v>
       </c>
-      <c r="I335" t="s">
+      <c r="K335" t="s">
         <v>27</v>
       </c>
-      <c r="J335" s="2"/>
-    </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L335" s="2"/>
+    </row>
+    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>34</v>
       </c>
@@ -10453,14 +12471,20 @@
         <v>56</v>
       </c>
       <c r="H336">
+        <v>3</v>
+      </c>
+      <c r="I336">
+        <v>0</v>
+      </c>
+      <c r="J336">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I336" t="s">
+      <c r="K336" t="s">
         <v>37</v>
       </c>
-      <c r="J336" s="2"/>
-    </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L336" s="2"/>
+    </row>
+    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>34</v>
       </c>
@@ -10483,14 +12507,20 @@
         <v>28</v>
       </c>
       <c r="H337">
+        <v>1</v>
+      </c>
+      <c r="I337">
+        <v>2</v>
+      </c>
+      <c r="J337">
         <v>2.4</v>
       </c>
-      <c r="I337" t="s">
+      <c r="K337" t="s">
         <v>9</v>
       </c>
-      <c r="J337" s="2"/>
-    </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L337" s="2"/>
+    </row>
+    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>34</v>
       </c>
@@ -10513,14 +12543,20 @@
         <v>56</v>
       </c>
       <c r="H338">
+        <v>3</v>
+      </c>
+      <c r="I338">
+        <v>0</v>
+      </c>
+      <c r="J338">
         <v>0.1</v>
       </c>
-      <c r="I338" t="s">
+      <c r="K338" t="s">
         <v>12</v>
       </c>
-      <c r="J338" s="2"/>
-    </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L338" s="2"/>
+    </row>
+    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>34</v>
       </c>
@@ -10543,14 +12579,20 @@
         <v>22</v>
       </c>
       <c r="H339">
+        <v>1</v>
+      </c>
+      <c r="I339">
+        <v>1</v>
+      </c>
+      <c r="J339">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I339" t="s">
+      <c r="K339" t="s">
         <v>7</v>
       </c>
-      <c r="J339" s="2"/>
-    </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L339" s="2"/>
+    </row>
+    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>34</v>
       </c>
@@ -10573,12 +12615,54 @@
         <v>81</v>
       </c>
       <c r="H340">
+        <v>5</v>
+      </c>
+      <c r="I340">
+        <v>1</v>
+      </c>
+      <c r="J340">
         <v>0.5</v>
       </c>
-      <c r="I340" t="s">
+      <c r="K340" t="s">
         <v>38</v>
       </c>
-      <c r="J340" s="2"/>
+      <c r="L340" s="2"/>
+    </row>
+    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <v>34</v>
+      </c>
+      <c r="B341" t="s">
+        <v>70</v>
+      </c>
+      <c r="C341" s="1">
+        <v>45778</v>
+      </c>
+      <c r="D341" t="s">
+        <v>65</v>
+      </c>
+      <c r="E341" t="s">
+        <v>21</v>
+      </c>
+      <c r="F341">
+        <v>0.9</v>
+      </c>
+      <c r="G341" t="s">
+        <v>13</v>
+      </c>
+      <c r="H341">
+        <v>0</v>
+      </c>
+      <c r="I341">
+        <v>2</v>
+      </c>
+      <c r="J341">
+        <v>1.3</v>
+      </c>
+      <c r="K341" t="s">
+        <v>31</v>
+      </c>
+      <c r="L341" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
@@ -10588,10 +12672,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F15253A6-5A08-48CB-B2F0-10236C66CD3C}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>34</v>
       </c>
@@ -10610,29 +12694,32 @@
       <c r="F1">
         <v>1.3</v>
       </c>
-      <c r="G1" t="s">
-        <v>32</v>
+      <c r="G1">
+        <v>2</v>
       </c>
       <c r="H1">
+        <v>1</v>
+      </c>
+      <c r="J1">
         <v>1.8</v>
       </c>
-      <c r="I1" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="2">
+      <c r="K1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="2">
         <v>51834</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>84</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>85</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>34</v>
       </c>
@@ -10651,29 +12738,32 @@
       <c r="F2">
         <v>1.2</v>
       </c>
-      <c r="G2" t="s">
-        <v>53</v>
+      <c r="G2">
+        <v>2</v>
       </c>
       <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="J2">
         <v>1.7</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="2">
+      <c r="L2" s="2">
         <v>60167</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>87</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>88</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>34</v>
       </c>
@@ -10692,29 +12782,32 @@
       <c r="F3">
         <v>0.8</v>
       </c>
-      <c r="G3" t="s">
-        <v>8</v>
+      <c r="G3">
+        <v>1</v>
       </c>
       <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>0.4</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="2">
+      <c r="L3" s="2">
         <v>39894</v>
       </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
         <v>89</v>
       </c>
-      <c r="L3" t="s">
+      <c r="N3" t="s">
         <v>90</v>
       </c>
-      <c r="M3" t="s">
+      <c r="O3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>34</v>
       </c>
@@ -10733,29 +12826,32 @@
       <c r="F4">
         <v>1.3</v>
       </c>
-      <c r="G4" t="s">
-        <v>55</v>
+      <c r="G4">
+        <v>3</v>
       </c>
       <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="J4">
         <v>1.3</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="2">
+      <c r="L4" s="2">
         <v>31499</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
         <v>91</v>
       </c>
-      <c r="L4" t="s">
+      <c r="N4" t="s">
         <v>92</v>
       </c>
-      <c r="M4" t="s">
+      <c r="O4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>34</v>
       </c>
@@ -10774,29 +12870,32 @@
       <c r="F5">
         <v>2</v>
       </c>
-      <c r="G5" t="s">
-        <v>56</v>
+      <c r="G5">
+        <v>3</v>
       </c>
       <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="J5">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="2">
+      <c r="L5" s="2">
         <v>31518</v>
       </c>
-      <c r="K5" t="s">
+      <c r="M5" t="s">
         <v>93</v>
       </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
         <v>94</v>
       </c>
-      <c r="M5" t="s">
+      <c r="O5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>34</v>
       </c>
@@ -10815,29 +12914,32 @@
       <c r="F6">
         <v>0.6</v>
       </c>
-      <c r="G6" t="s">
-        <v>28</v>
+      <c r="G6">
+        <v>1</v>
       </c>
       <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
         <v>2.4</v>
       </c>
-      <c r="I6" t="s">
+      <c r="K6" t="s">
         <v>9</v>
       </c>
-      <c r="J6" s="2">
+      <c r="L6" s="2">
         <v>28946</v>
       </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>95</v>
       </c>
-      <c r="L6" t="s">
+      <c r="N6" t="s">
         <v>96</v>
       </c>
-      <c r="M6" t="s">
+      <c r="O6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>34</v>
       </c>
@@ -10856,29 +12958,32 @@
       <c r="F7">
         <v>2.4</v>
       </c>
-      <c r="G7" t="s">
-        <v>56</v>
+      <c r="G7">
+        <v>3</v>
       </c>
       <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>0.1</v>
       </c>
-      <c r="I7" t="s">
+      <c r="K7" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>52171</v>
       </c>
-      <c r="K7" t="s">
+      <c r="M7" t="s">
         <v>97</v>
       </c>
-      <c r="L7" t="s">
+      <c r="N7" t="s">
         <v>88</v>
       </c>
-      <c r="M7" t="s">
+      <c r="O7" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>34</v>
       </c>
@@ -10897,29 +13002,32 @@
       <c r="F8">
         <v>0.5</v>
       </c>
-      <c r="G8" t="s">
-        <v>22</v>
+      <c r="G8">
+        <v>1</v>
       </c>
       <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="J8">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I8" t="s">
+      <c r="K8" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="2">
+      <c r="L8" s="2">
         <v>11241</v>
       </c>
-      <c r="K8" t="s">
+      <c r="M8" t="s">
         <v>98</v>
       </c>
-      <c r="L8" t="s">
+      <c r="N8" t="s">
         <v>99</v>
       </c>
-      <c r="M8" t="s">
+      <c r="O8" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>34</v>
       </c>
@@ -10938,25 +13046,28 @@
       <c r="F9">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G9" t="s">
-        <v>81</v>
+      <c r="G9">
+        <v>5</v>
       </c>
       <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="J9">
         <v>0.5</v>
       </c>
-      <c r="I9" t="s">
+      <c r="K9" t="s">
         <v>38</v>
       </c>
-      <c r="J9" s="2">
+      <c r="L9" s="2">
         <v>60415</v>
       </c>
-      <c r="K9" t="s">
+      <c r="M9" t="s">
         <v>100</v>
       </c>
-      <c r="L9" t="s">
+      <c r="N9" t="s">
         <v>101</v>
       </c>
-      <c r="M9" t="s">
+      <c r="O9" t="s">
         <v>86</v>
       </c>
     </row>

--- a/data/premier_league_raw_match_data.xlsx
+++ b/data/premier_league_raw_match_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Desktop\InStatsWeTrust\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487575A5-4331-40B3-BAE5-B01D671FAF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886F6A6C-E158-4973-BC3D-B043E82E0A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21150" xr2:uid="{0FE85BFC-2024-4027-B3AD-B7D6B58B61DA}"/>
+    <workbookView xWindow="-28245" yWindow="2325" windowWidth="25875" windowHeight="13455" xr2:uid="{0FE85BFC-2024-4027-B3AD-B7D6B58B61DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1864" uniqueCount="106">
   <si>
     <t>Manchester City</t>
   </si>
@@ -333,6 +333,12 @@
   </si>
   <si>
     <t>Goals_Against</t>
+  </si>
+  <si>
+    <t>12:00 (13:00)</t>
+  </si>
+  <si>
+    <t>14:15 (15:15)</t>
   </si>
 </sst>
 </file>
@@ -705,14 +711,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A647DF9E-0117-4165-BE47-DD1C6849A118}">
-  <dimension ref="A1:L341"/>
+  <dimension ref="A1:L361"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.140625" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" customWidth="1"/>
     <col min="7" max="7" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -12663,6 +12669,556 @@
         <v>31</v>
       </c>
       <c r="L341" s="2"/>
+    </row>
+    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A342">
+        <v>35</v>
+      </c>
+      <c r="B342" t="s">
+        <v>5</v>
+      </c>
+      <c r="C342" s="1">
+        <v>45779</v>
+      </c>
+      <c r="D342" t="s">
+        <v>6</v>
+      </c>
+      <c r="E342" t="s">
+        <v>0</v>
+      </c>
+      <c r="F342">
+        <v>0.7</v>
+      </c>
+      <c r="G342" t="s">
+        <v>8</v>
+      </c>
+      <c r="H342">
+        <v>1</v>
+      </c>
+      <c r="I342">
+        <v>0</v>
+      </c>
+      <c r="J342">
+        <v>0.4</v>
+      </c>
+      <c r="K342" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A343">
+        <v>35</v>
+      </c>
+      <c r="B343" t="s">
+        <v>10</v>
+      </c>
+      <c r="C343" s="1">
+        <v>45780</v>
+      </c>
+      <c r="D343" t="s">
+        <v>11</v>
+      </c>
+      <c r="E343" t="s">
+        <v>1</v>
+      </c>
+      <c r="F343">
+        <v>1</v>
+      </c>
+      <c r="G343" t="s">
+        <v>8</v>
+      </c>
+      <c r="H343">
+        <v>1</v>
+      </c>
+      <c r="I343">
+        <v>0</v>
+      </c>
+      <c r="J343">
+        <v>0.9</v>
+      </c>
+      <c r="K343" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A344">
+        <v>35</v>
+      </c>
+      <c r="B344" t="s">
+        <v>10</v>
+      </c>
+      <c r="C344" s="1">
+        <v>45780</v>
+      </c>
+      <c r="D344" t="s">
+        <v>15</v>
+      </c>
+      <c r="E344" t="s">
+        <v>37</v>
+      </c>
+      <c r="F344">
+        <v>1.4</v>
+      </c>
+      <c r="G344" t="s">
+        <v>24</v>
+      </c>
+      <c r="H344">
+        <v>2</v>
+      </c>
+      <c r="I344">
+        <v>0</v>
+      </c>
+      <c r="J344">
+        <v>0.5</v>
+      </c>
+      <c r="K344" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A345">
+        <v>35</v>
+      </c>
+      <c r="B345" t="s">
+        <v>10</v>
+      </c>
+      <c r="C345" s="1">
+        <v>45780</v>
+      </c>
+      <c r="D345" t="s">
+        <v>15</v>
+      </c>
+      <c r="E345" t="s">
+        <v>18</v>
+      </c>
+      <c r="F345">
+        <v>0.6</v>
+      </c>
+      <c r="G345" t="s">
+        <v>53</v>
+      </c>
+      <c r="H345">
+        <v>2</v>
+      </c>
+      <c r="I345">
+        <v>2</v>
+      </c>
+      <c r="J345">
+        <v>0.8</v>
+      </c>
+      <c r="K345" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A346">
+        <v>35</v>
+      </c>
+      <c r="B346" t="s">
+        <v>10</v>
+      </c>
+      <c r="C346" s="1">
+        <v>45780</v>
+      </c>
+      <c r="D346" t="s">
+        <v>26</v>
+      </c>
+      <c r="E346" t="s">
+        <v>2</v>
+      </c>
+      <c r="F346">
+        <v>1.4</v>
+      </c>
+      <c r="G346" t="s">
+        <v>28</v>
+      </c>
+      <c r="H346">
+        <v>1</v>
+      </c>
+      <c r="I346">
+        <v>2</v>
+      </c>
+      <c r="J346">
+        <v>0.9</v>
+      </c>
+      <c r="K346" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A347">
+        <v>35</v>
+      </c>
+      <c r="B347" t="s">
+        <v>29</v>
+      </c>
+      <c r="C347" s="1">
+        <v>45781</v>
+      </c>
+      <c r="D347" t="s">
+        <v>30</v>
+      </c>
+      <c r="E347" t="s">
+        <v>20</v>
+      </c>
+      <c r="F347">
+        <v>0.7</v>
+      </c>
+      <c r="G347" t="s">
+        <v>22</v>
+      </c>
+      <c r="H347">
+        <v>1</v>
+      </c>
+      <c r="I347">
+        <v>1</v>
+      </c>
+      <c r="J347">
+        <v>1.7</v>
+      </c>
+      <c r="K347" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A348">
+        <v>35</v>
+      </c>
+      <c r="B348" t="s">
+        <v>29</v>
+      </c>
+      <c r="C348" s="1">
+        <v>45781</v>
+      </c>
+      <c r="D348" t="s">
+        <v>30</v>
+      </c>
+      <c r="E348" t="s">
+        <v>27</v>
+      </c>
+      <c r="F348">
+        <v>0.8</v>
+      </c>
+      <c r="G348" t="s">
+        <v>22</v>
+      </c>
+      <c r="H348">
+        <v>1</v>
+      </c>
+      <c r="I348">
+        <v>1</v>
+      </c>
+      <c r="J348">
+        <v>0.8</v>
+      </c>
+      <c r="K348" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A349">
+        <v>35</v>
+      </c>
+      <c r="B349" t="s">
+        <v>29</v>
+      </c>
+      <c r="C349" s="1">
+        <v>45781</v>
+      </c>
+      <c r="D349" t="s">
+        <v>30</v>
+      </c>
+      <c r="E349" t="s">
+        <v>31</v>
+      </c>
+      <c r="F349">
+        <v>2.8</v>
+      </c>
+      <c r="G349" t="s">
+        <v>59</v>
+      </c>
+      <c r="H349">
+        <v>4</v>
+      </c>
+      <c r="I349">
+        <v>3</v>
+      </c>
+      <c r="J349">
+        <v>1.5</v>
+      </c>
+      <c r="K349" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A350">
+        <v>35</v>
+      </c>
+      <c r="B350" t="s">
+        <v>29</v>
+      </c>
+      <c r="C350" s="1">
+        <v>45781</v>
+      </c>
+      <c r="D350" t="s">
+        <v>34</v>
+      </c>
+      <c r="E350" t="s">
+        <v>35</v>
+      </c>
+      <c r="F350">
+        <v>3.1</v>
+      </c>
+      <c r="G350" t="s">
+        <v>48</v>
+      </c>
+      <c r="H350">
+        <v>3</v>
+      </c>
+      <c r="I350">
+        <v>1</v>
+      </c>
+      <c r="J350">
+        <v>1</v>
+      </c>
+      <c r="K350" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A351">
+        <v>35</v>
+      </c>
+      <c r="B351" t="s">
+        <v>36</v>
+      </c>
+      <c r="C351" s="1">
+        <v>45782</v>
+      </c>
+      <c r="D351" t="s">
+        <v>6</v>
+      </c>
+      <c r="E351" t="s">
+        <v>33</v>
+      </c>
+      <c r="F351">
+        <v>2.5</v>
+      </c>
+      <c r="G351" t="s">
+        <v>22</v>
+      </c>
+      <c r="H351">
+        <v>1</v>
+      </c>
+      <c r="I351">
+        <v>1</v>
+      </c>
+      <c r="J351">
+        <v>0.7</v>
+      </c>
+      <c r="K351" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A352">
+        <v>36</v>
+      </c>
+      <c r="B352" t="s">
+        <v>10</v>
+      </c>
+      <c r="C352" s="1">
+        <v>45787</v>
+      </c>
+      <c r="D352" t="s">
+        <v>15</v>
+      </c>
+      <c r="E352" t="s">
+        <v>12</v>
+      </c>
+      <c r="K352" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A353">
+        <v>36</v>
+      </c>
+      <c r="B353" t="s">
+        <v>10</v>
+      </c>
+      <c r="C353" s="1">
+        <v>45787</v>
+      </c>
+      <c r="D353" t="s">
+        <v>15</v>
+      </c>
+      <c r="E353" t="s">
+        <v>9</v>
+      </c>
+      <c r="K353" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A354">
+        <v>36</v>
+      </c>
+      <c r="B354" t="s">
+        <v>10</v>
+      </c>
+      <c r="C354" s="1">
+        <v>45787</v>
+      </c>
+      <c r="D354" t="s">
+        <v>15</v>
+      </c>
+      <c r="E354" t="s">
+        <v>25</v>
+      </c>
+      <c r="K354" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>36</v>
+      </c>
+      <c r="B355" t="s">
+        <v>10</v>
+      </c>
+      <c r="C355" s="1">
+        <v>45787</v>
+      </c>
+      <c r="D355" t="s">
+        <v>15</v>
+      </c>
+      <c r="E355" t="s">
+        <v>17</v>
+      </c>
+      <c r="K355" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <v>36</v>
+      </c>
+      <c r="B356" t="s">
+        <v>10</v>
+      </c>
+      <c r="C356" s="1">
+        <v>45787</v>
+      </c>
+      <c r="D356" t="s">
+        <v>26</v>
+      </c>
+      <c r="E356" t="s">
+        <v>23</v>
+      </c>
+      <c r="K356" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A357">
+        <v>36</v>
+      </c>
+      <c r="B357" t="s">
+        <v>29</v>
+      </c>
+      <c r="C357" s="1">
+        <v>45788</v>
+      </c>
+      <c r="D357" t="s">
+        <v>104</v>
+      </c>
+      <c r="E357" t="s">
+        <v>16</v>
+      </c>
+      <c r="K357" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A358">
+        <v>36</v>
+      </c>
+      <c r="B358" t="s">
+        <v>29</v>
+      </c>
+      <c r="C358" s="1">
+        <v>45788</v>
+      </c>
+      <c r="D358" t="s">
+        <v>105</v>
+      </c>
+      <c r="E358" t="s">
+        <v>21</v>
+      </c>
+      <c r="K358" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A359">
+        <v>36</v>
+      </c>
+      <c r="B359" t="s">
+        <v>29</v>
+      </c>
+      <c r="C359" s="1">
+        <v>45788</v>
+      </c>
+      <c r="D359" t="s">
+        <v>105</v>
+      </c>
+      <c r="E359" t="s">
+        <v>38</v>
+      </c>
+      <c r="K359" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A360">
+        <v>36</v>
+      </c>
+      <c r="B360" t="s">
+        <v>29</v>
+      </c>
+      <c r="C360" s="1">
+        <v>45788</v>
+      </c>
+      <c r="D360" t="s">
+        <v>105</v>
+      </c>
+      <c r="E360" t="s">
+        <v>7</v>
+      </c>
+      <c r="K360" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A361">
+        <v>36</v>
+      </c>
+      <c r="B361" t="s">
+        <v>29</v>
+      </c>
+      <c r="C361" s="1">
+        <v>45788</v>
+      </c>
+      <c r="D361" t="s">
+        <v>34</v>
+      </c>
+      <c r="E361" t="s">
+        <v>14</v>
+      </c>
+      <c r="K361" t="s">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
